--- a/FAZENDA_PANAMA_distancias.xlsx
+++ b/FAZENDA_PANAMA_distancias.xlsx
@@ -617,10 +617,10 @@
         <v>4875</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>7675</v>
+        <v>7066</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>5617</v>
+        <v>5034</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>3796</v>
@@ -652,10 +652,10 @@
         <v>5893</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>7280</v>
+        <v>6677</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>4503</v>
+        <v>3919</v>
       </c>
       <c r="F6" s="14" t="n">
         <v>2870</v>
@@ -687,10 +687,10 @@
         <v>4651</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>6928</v>
+        <v>6168</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>4604</v>
+        <v>3849</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>3350</v>
@@ -710,39 +710,39 @@
       <c r="J7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>T-09</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n">
+      <c r="B8" s="12" t="n">
         <v>185.59</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="13" t="n">
         <v>6451</v>
       </c>
-      <c r="D8" s="21" t="n">
-        <v>6640</v>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>3419</v>
-      </c>
-      <c r="F8" s="21" t="n">
+      <c r="D8" s="14" t="n">
+        <v>6028</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>2836</v>
+      </c>
+      <c r="F8" s="14" t="n">
         <v>2159</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="15">
         <f>D8/1000</f>
         <v/>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="15">
         <f>E8/1000</f>
         <v/>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="16">
         <f>IFERROR(D8/F8,"")</f>
         <v/>
       </c>
-      <c r="J8" s="24" t="inlineStr"/>
+      <c r="J8" s="17" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -757,10 +757,10 @@
         <v>4667</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>6069</v>
+        <v>5629</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>3748</v>
+        <v>3476</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>3453</v>
@@ -782,23 +782,23 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>P-22</t>
+          <t>T-01</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>104.48</v>
+        <v>59.49</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>4116</v>
+        <v>4192</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>5797</v>
+        <v>5466</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>3752</v>
+        <v>3476</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>2549</v>
+        <v>3468</v>
       </c>
       <c r="G10" s="15">
         <f>D10/1000</f>
@@ -817,23 +817,23 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>P-19</t>
+          <t>T-05</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>128.74</v>
+        <v>205.66</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4709</v>
+        <v>5951</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>5774</v>
+        <v>5178</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3648</v>
+        <v>2371</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>2722</v>
+        <v>2356</v>
       </c>
       <c r="G11" s="8">
         <f>D11/1000</f>
@@ -850,60 +850,60 @@
       <c r="J11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>T-12</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="n">
-        <v>141.49</v>
-      </c>
-      <c r="C12" s="20" t="n">
-        <v>7024</v>
-      </c>
-      <c r="D12" s="21" t="n">
-        <v>5608</v>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>2765</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>1843</v>
-      </c>
-      <c r="G12" s="22">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>T-04</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>205.61</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>5931</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>5130</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>2375</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>2368</v>
+      </c>
+      <c r="G12" s="15">
         <f>D12/1000</f>
         <v/>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="15">
         <f>E12/1000</f>
         <v/>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="16">
         <f>IFERROR(D12/F12,"")</f>
         <v/>
       </c>
-      <c r="J12" s="24" t="inlineStr"/>
+      <c r="J12" s="17" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>T-05</t>
+          <t>P-22</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>205.66</v>
+        <v>104.48</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>5951</v>
+        <v>4116</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>5604</v>
+        <v>5041</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>2641</v>
+        <v>2997</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>2356</v>
+        <v>2549</v>
       </c>
       <c r="G13" s="8">
         <f>D13/1000</f>
@@ -922,23 +922,23 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>T-01</t>
+          <t>P-19</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>59.49</v>
+        <v>128.74</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>4192</v>
+        <v>4709</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>5603</v>
+        <v>4942</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>3748</v>
+        <v>2755</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>3468</v>
+        <v>2722</v>
       </c>
       <c r="G14" s="15">
         <f>D14/1000</f>
@@ -957,23 +957,23 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>T-04</t>
+          <t>T-12</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>205.61</v>
+        <v>141.49</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>5931</v>
+        <v>7024</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>5260</v>
+        <v>4900</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>2647</v>
+        <v>1983</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>2368</v>
+        <v>1843</v>
       </c>
       <c r="G15" s="8">
         <f>D15/1000</f>
@@ -992,23 +992,23 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>T-14</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>111.43</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>5109</v>
+        <v>4914</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>5228</v>
+        <v>4389</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>2897</v>
+        <v>2007</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>1838</v>
+        <v>1828</v>
       </c>
       <c r="G16" s="15">
         <f>D16/1000</f>
@@ -1027,23 +1027,23 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>T-14</t>
+          <t>P-15</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>81.06999999999999</v>
+        <v>111.43</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>4914</v>
+        <v>5109</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>5197</v>
+        <v>4331</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>2790</v>
+        <v>1998</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>1828</v>
+        <v>1838</v>
       </c>
       <c r="G17" s="8">
         <f>D17/1000</f>
@@ -1072,10 +1072,10 @@
         <v>5923</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>4503</v>
+        <v>4071</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>1553</v>
+        <v>1283</v>
       </c>
       <c r="F18" s="21" t="n">
         <v>1272</v>
@@ -1097,23 +1097,23 @@
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>P-18</t>
+          <t>T-07</t>
         </is>
       </c>
       <c r="B19" s="19" t="n">
-        <v>136.31</v>
+        <v>200.1</v>
       </c>
       <c r="C19" s="20" t="n">
-        <v>4890</v>
+        <v>5875</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>4310</v>
+        <v>4022</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>1941</v>
+        <v>1283</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>1018</v>
+        <v>1280</v>
       </c>
       <c r="G19" s="22">
         <f>D19/1000</f>
@@ -1132,23 +1132,23 @@
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>T-07</t>
+          <t>P-18</t>
         </is>
       </c>
       <c r="B20" s="19" t="n">
-        <v>200.1</v>
+        <v>136.31</v>
       </c>
       <c r="C20" s="20" t="n">
-        <v>5875</v>
+        <v>4890</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>4155</v>
+        <v>3427</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>1553</v>
+        <v>1048</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>1280</v>
+        <v>1018</v>
       </c>
       <c r="G20" s="22">
         <f>D20/1000</f>
@@ -1167,23 +1167,23 @@
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>P-21</t>
+          <t>P-20</t>
         </is>
       </c>
       <c r="B21" s="19" t="n">
-        <v>148.24</v>
+        <v>115.16</v>
       </c>
       <c r="C21" s="20" t="n">
-        <v>4904</v>
+        <v>4391</v>
       </c>
       <c r="D21" s="21" t="n">
-        <v>3677</v>
+        <v>3412</v>
       </c>
       <c r="E21" s="21" t="n">
-        <v>1237</v>
+        <v>1247</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>1045</v>
+        <v>1059</v>
       </c>
       <c r="G21" s="22">
         <f>D21/1000</f>
@@ -1202,23 +1202,23 @@
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>T-11</t>
+          <t>P-21</t>
         </is>
       </c>
       <c r="B22" s="19" t="n">
-        <v>181.52</v>
+        <v>148.24</v>
       </c>
       <c r="C22" s="20" t="n">
-        <v>7622</v>
+        <v>4904</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>3484</v>
+        <v>3407</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>679</v>
+        <v>1251</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>258</v>
+        <v>1045</v>
       </c>
       <c r="G22" s="22">
         <f>D22/1000</f>
@@ -1237,23 +1237,23 @@
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>P-20</t>
+          <t>T-11</t>
         </is>
       </c>
       <c r="B23" s="19" t="n">
-        <v>115.16</v>
+        <v>181.52</v>
       </c>
       <c r="C23" s="20" t="n">
-        <v>4391</v>
+        <v>7622</v>
       </c>
       <c r="D23" s="21" t="n">
-        <v>3403</v>
+        <v>2952</v>
       </c>
       <c r="E23" s="21" t="n">
-        <v>1235</v>
+        <v>408</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>1059</v>
+        <v>258</v>
       </c>
       <c r="G23" s="22">
         <f>D23/1000</f>
@@ -1272,23 +1272,23 @@
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>T-13</t>
+          <t>T-10</t>
         </is>
       </c>
       <c r="B24" s="19" t="n">
-        <v>56.86</v>
+        <v>171.85</v>
       </c>
       <c r="C24" s="20" t="n">
-        <v>4026</v>
+        <v>5764</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>3126</v>
+        <v>2897</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>1247</v>
+        <v>175</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>308</v>
+        <v>154</v>
       </c>
       <c r="G24" s="22">
         <f>D24/1000</f>
@@ -1307,23 +1307,23 @@
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>T-10</t>
+          <t>T-16</t>
         </is>
       </c>
       <c r="B25" s="19" t="n">
-        <v>171.85</v>
+        <v>70.63</v>
       </c>
       <c r="C25" s="20" t="n">
-        <v>5764</v>
+        <v>4030</v>
       </c>
       <c r="D25" s="21" t="n">
-        <v>3033</v>
+        <v>2762</v>
       </c>
       <c r="E25" s="21" t="n">
-        <v>155</v>
+        <v>777</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>154</v>
+        <v>591</v>
       </c>
       <c r="G25" s="22">
         <f>D25/1000</f>
@@ -1342,23 +1342,23 @@
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>P-17</t>
+          <t>P-16</t>
         </is>
       </c>
       <c r="B26" s="19" t="n">
-        <v>113.44</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="C26" s="20" t="n">
-        <v>4389</v>
+        <v>4729</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>2834</v>
+        <v>2556</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>652</v>
+        <v>194</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>240</v>
+        <v>179</v>
       </c>
       <c r="G26" s="22">
         <f>D26/1000</f>
@@ -1377,23 +1377,23 @@
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>T-16</t>
+          <t>T-13</t>
         </is>
       </c>
       <c r="B27" s="19" t="n">
-        <v>70.63</v>
+        <v>56.86</v>
       </c>
       <c r="C27" s="20" t="n">
-        <v>4030</v>
+        <v>4026</v>
       </c>
       <c r="D27" s="21" t="n">
-        <v>2748</v>
+        <v>2281</v>
       </c>
       <c r="E27" s="21" t="n">
-        <v>763</v>
+        <v>352</v>
       </c>
       <c r="F27" s="21" t="n">
-        <v>591</v>
+        <v>308</v>
       </c>
       <c r="G27" s="22">
         <f>D27/1000</f>
@@ -1412,23 +1412,23 @@
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>P-16</t>
+          <t>P-17</t>
         </is>
       </c>
       <c r="B28" s="19" t="n">
-        <v>94.93000000000001</v>
+        <v>113.44</v>
       </c>
       <c r="C28" s="20" t="n">
-        <v>4729</v>
+        <v>4389</v>
       </c>
       <c r="D28" s="21" t="n">
-        <v>2542</v>
+        <v>2267</v>
       </c>
       <c r="E28" s="21" t="n">
-        <v>180</v>
+        <v>267</v>
       </c>
       <c r="F28" s="21" t="n">
-        <v>179</v>
+        <v>240</v>
       </c>
       <c r="G28" s="22">
         <f>D28/1000</f>

--- a/FAZENDA_PANAMA_distancias.xlsx
+++ b/FAZENDA_PANAMA_distancias.xlsx
@@ -607,23 +607,23 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>T-03</t>
+          <t>P-23</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>73.69</v>
+        <v>126.4</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>4875</v>
+        <v>4651</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>7066</v>
+        <v>8314</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>5034</v>
+        <v>3916</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>3796</v>
+        <v>3350</v>
       </c>
       <c r="G5" s="8">
         <f>D5/1000</f>
@@ -642,23 +642,23 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>T-06</t>
+          <t>T-03</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>165.19</v>
+        <v>73.69</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>5893</v>
+        <v>4875</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>6677</v>
+        <v>7290</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>3919</v>
+        <v>5147</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>2870</v>
+        <v>3796</v>
       </c>
       <c r="G6" s="15">
         <f>D6/1000</f>
@@ -677,23 +677,23 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>P-23</t>
+          <t>T-06</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>126.4</v>
+        <v>165.19</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>4651</v>
+        <v>5893</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>6168</v>
+        <v>7290</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>3849</v>
+        <v>4032</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3350</v>
+        <v>2870</v>
       </c>
       <c r="G7" s="8">
         <f>D7/1000</f>
@@ -712,23 +712,23 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>T-09</t>
+          <t>P-19</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>185.59</v>
+        <v>128.74</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>6451</v>
+        <v>4709</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>6028</v>
+        <v>6875</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>2836</v>
+        <v>2759</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>2159</v>
+        <v>2722</v>
       </c>
       <c r="G8" s="15">
         <f>D8/1000</f>
@@ -747,23 +747,23 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>T-09</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>93.91</v>
+        <v>185.59</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>4667</v>
+        <v>6451</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>5629</v>
+        <v>6181</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>3476</v>
+        <v>2949</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>3453</v>
+        <v>2159</v>
       </c>
       <c r="G9" s="8">
         <f>D9/1000</f>
@@ -782,23 +782,23 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>T-01</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>59.49</v>
+        <v>93.91</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>4192</v>
+        <v>4667</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>5466</v>
+        <v>5916</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>3476</v>
+        <v>3852</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>3468</v>
+        <v>3453</v>
       </c>
       <c r="G10" s="15">
         <f>D10/1000</f>
@@ -827,7 +827,7 @@
         <v>5951</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>5178</v>
+        <v>5916</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>2371</v>
@@ -850,60 +850,60 @@
       <c r="J11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>T-04</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n">
-        <v>205.61</v>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>5931</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>5130</v>
-      </c>
-      <c r="E12" s="14" t="n">
-        <v>2375</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>2368</v>
-      </c>
-      <c r="G12" s="15">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>P-15</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>111.43</v>
+      </c>
+      <c r="C12" s="20" t="n">
+        <v>5109</v>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>5865</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>1998</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>1838</v>
+      </c>
+      <c r="G12" s="22">
         <f>D12/1000</f>
         <v/>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="22">
         <f>E12/1000</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="23">
         <f>IFERROR(D12/F12,"")</f>
         <v/>
       </c>
-      <c r="J12" s="17" t="inlineStr"/>
+      <c r="J12" s="24" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>P-22</t>
+          <t>T-01</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>104.48</v>
+        <v>59.49</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>4116</v>
+        <v>4192</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>5041</v>
+        <v>5844</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>2997</v>
+        <v>3852</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>2549</v>
+        <v>3468</v>
       </c>
       <c r="G13" s="8">
         <f>D13/1000</f>
@@ -922,23 +922,23 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>P-19</t>
+          <t>T-04</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>128.74</v>
+        <v>205.61</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>4709</v>
+        <v>5931</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>4942</v>
+        <v>5844</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>2755</v>
+        <v>2375</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>2722</v>
+        <v>2368</v>
       </c>
       <c r="G14" s="15">
         <f>D14/1000</f>
@@ -957,23 +957,23 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>T-12</t>
+          <t>P-22</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>141.49</v>
+        <v>104.48</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>7024</v>
+        <v>4116</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>4900</v>
+        <v>5660</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1983</v>
+        <v>3557</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>1843</v>
+        <v>2549</v>
       </c>
       <c r="G15" s="8">
         <f>D15/1000</f>
@@ -1002,10 +1002,10 @@
         <v>4914</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>4389</v>
+        <v>5255</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>2007</v>
+        <v>2109</v>
       </c>
       <c r="F16" s="14" t="n">
         <v>1828</v>
@@ -1027,23 +1027,23 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>P-15</t>
+          <t>T-12</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>111.43</v>
+        <v>141.49</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>5109</v>
+        <v>7024</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>4331</v>
+        <v>5026</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1998</v>
+        <v>2073</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>1838</v>
+        <v>1843</v>
       </c>
       <c r="G17" s="8">
         <f>D17/1000</f>
@@ -1062,23 +1062,23 @@
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>T-08</t>
+          <t>T-07</t>
         </is>
       </c>
       <c r="B18" s="19" t="n">
-        <v>202.95</v>
+        <v>200.1</v>
       </c>
       <c r="C18" s="20" t="n">
-        <v>5923</v>
+        <v>5875</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>4071</v>
+        <v>4714</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>1272</v>
+        <v>1280</v>
       </c>
       <c r="G18" s="22">
         <f>D18/1000</f>
@@ -1097,23 +1097,23 @@
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>T-07</t>
+          <t>T-08</t>
         </is>
       </c>
       <c r="B19" s="19" t="n">
-        <v>200.1</v>
+        <v>202.95</v>
       </c>
       <c r="C19" s="20" t="n">
-        <v>5875</v>
+        <v>5923</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>4022</v>
+        <v>4612</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>1280</v>
+        <v>1272</v>
       </c>
       <c r="G19" s="22">
         <f>D19/1000</f>
@@ -1132,23 +1132,23 @@
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>P-18</t>
+          <t>P-20</t>
         </is>
       </c>
       <c r="B20" s="19" t="n">
-        <v>136.31</v>
+        <v>115.16</v>
       </c>
       <c r="C20" s="20" t="n">
-        <v>4890</v>
+        <v>4391</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>3427</v>
+        <v>4250</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>1048</v>
+        <v>1375</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>1018</v>
+        <v>1059</v>
       </c>
       <c r="G20" s="22">
         <f>D20/1000</f>
@@ -1167,23 +1167,23 @@
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>P-20</t>
+          <t>P-18</t>
         </is>
       </c>
       <c r="B21" s="19" t="n">
-        <v>115.16</v>
+        <v>136.31</v>
       </c>
       <c r="C21" s="20" t="n">
-        <v>4391</v>
+        <v>4890</v>
       </c>
       <c r="D21" s="21" t="n">
-        <v>3412</v>
+        <v>3876</v>
       </c>
       <c r="E21" s="21" t="n">
-        <v>1247</v>
+        <v>1063</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>1059</v>
+        <v>1018</v>
       </c>
       <c r="G21" s="22">
         <f>D21/1000</f>
@@ -1212,10 +1212,10 @@
         <v>4904</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>3407</v>
+        <v>3549</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>1251</v>
+        <v>1384</v>
       </c>
       <c r="F22" s="21" t="n">
         <v>1045</v>
@@ -1237,23 +1237,23 @@
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>T-11</t>
+          <t>T-16</t>
         </is>
       </c>
       <c r="B23" s="19" t="n">
-        <v>181.52</v>
+        <v>70.63</v>
       </c>
       <c r="C23" s="20" t="n">
-        <v>7622</v>
+        <v>4030</v>
       </c>
       <c r="D23" s="21" t="n">
-        <v>2952</v>
+        <v>3374</v>
       </c>
       <c r="E23" s="21" t="n">
-        <v>408</v>
+        <v>916</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>258</v>
+        <v>591</v>
       </c>
       <c r="G23" s="22">
         <f>D23/1000</f>
@@ -1272,23 +1272,23 @@
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>T-10</t>
+          <t>P-16</t>
         </is>
       </c>
       <c r="B24" s="19" t="n">
-        <v>171.85</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="C24" s="20" t="n">
-        <v>5764</v>
+        <v>4729</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>2897</v>
+        <v>3130</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="G24" s="22">
         <f>D24/1000</f>
@@ -1307,23 +1307,23 @@
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>T-16</t>
+          <t>T-11</t>
         </is>
       </c>
       <c r="B25" s="19" t="n">
-        <v>70.63</v>
+        <v>181.52</v>
       </c>
       <c r="C25" s="20" t="n">
-        <v>4030</v>
+        <v>7622</v>
       </c>
       <c r="D25" s="21" t="n">
-        <v>2762</v>
+        <v>3023</v>
       </c>
       <c r="E25" s="21" t="n">
-        <v>777</v>
+        <v>411</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>591</v>
+        <v>258</v>
       </c>
       <c r="G25" s="22">
         <f>D25/1000</f>
@@ -1342,23 +1342,23 @@
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>P-16</t>
+          <t>T-10</t>
         </is>
       </c>
       <c r="B26" s="19" t="n">
-        <v>94.93000000000001</v>
+        <v>171.85</v>
       </c>
       <c r="C26" s="20" t="n">
-        <v>4729</v>
+        <v>5764</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>2556</v>
+        <v>2943</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="G26" s="22">
         <f>D26/1000</f>
@@ -1387,7 +1387,7 @@
         <v>4026</v>
       </c>
       <c r="D27" s="21" t="n">
-        <v>2281</v>
+        <v>2923</v>
       </c>
       <c r="E27" s="21" t="n">
         <v>352</v>
@@ -1422,7 +1422,7 @@
         <v>4389</v>
       </c>
       <c r="D28" s="21" t="n">
-        <v>2267</v>
+        <v>2513</v>
       </c>
       <c r="E28" s="21" t="n">
         <v>267</v>

--- a/FAZENDA_PANAMA_distancias.xlsx
+++ b/FAZENDA_PANAMA_distancias.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33D7380-C115-40C7-98D8-83AA7F4D1033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B106930C-3E74-4437-9B74-957F5E6F1161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34755" yWindow="2610" windowWidth="17625" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1884" yWindow="1884" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>

--- a/FAZENDA_PANAMA_distancias.xlsx
+++ b/FAZENDA_PANAMA_distancias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B106930C-3E74-4437-9B74-957F5E6F1161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59CB5E9A-9BB7-49BB-BA0C-205A23E77096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1884" yWindow="1884" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/FAZENDA_PANAMA_distancias.xlsx
+++ b/FAZENDA_PANAMA_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59CB5E9A-9BB7-49BB-BA0C-205A23E77096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B40269-9DAF-4941-B7FD-0AB4DA4CE191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
   <si>
     <t>FAZENDA PANAMA — distância dos talhões até a sede</t>
   </si>
@@ -72,76 +72,85 @@
     <t>Observação</t>
   </si>
   <si>
+    <t>T-01</t>
+  </si>
+  <si>
+    <t>T-06</t>
+  </si>
+  <si>
+    <t>T-09</t>
+  </si>
+  <si>
+    <t>P-23</t>
+  </si>
+  <si>
+    <t>T-03</t>
+  </si>
+  <si>
+    <t>T-05</t>
+  </si>
+  <si>
+    <t>T-08</t>
+  </si>
+  <si>
+    <t>T-12</t>
+  </si>
+  <si>
+    <t>P-19</t>
+  </si>
+  <si>
+    <t>T-11</t>
+  </si>
+  <si>
     <t>T-02</t>
   </si>
   <si>
-    <t>T-05</t>
-  </si>
-  <si>
-    <t>T-03</t>
-  </si>
-  <si>
-    <t>T-06</t>
-  </si>
-  <si>
-    <t>P-23</t>
-  </si>
-  <si>
-    <t>T-08</t>
-  </si>
-  <si>
-    <t>T-09</t>
-  </si>
-  <si>
-    <t>P-19</t>
-  </si>
-  <si>
-    <t>T-11</t>
-  </si>
-  <si>
-    <t>T-12</t>
+    <t>T-07</t>
+  </si>
+  <si>
+    <t>T-04</t>
+  </si>
+  <si>
+    <t>P-15</t>
+  </si>
+  <si>
+    <t>P-20</t>
+  </si>
+  <si>
+    <t>T-14</t>
+  </si>
+  <si>
+    <t>T-10</t>
+  </si>
+  <si>
+    <t>P-16</t>
+  </si>
+  <si>
+    <t>P-21</t>
+  </si>
+  <si>
+    <t>T-13</t>
+  </si>
+  <si>
+    <t>P-18</t>
+  </si>
+  <si>
+    <t>T-16</t>
+  </si>
+  <si>
+    <t>P-17</t>
   </si>
   <si>
     <t>P-22</t>
   </si>
   <si>
-    <t>P-15</t>
-  </si>
-  <si>
-    <t>T-01</t>
-  </si>
-  <si>
-    <t>T-04</t>
-  </si>
-  <si>
-    <t>P-16</t>
-  </si>
-  <si>
-    <t>T-14</t>
-  </si>
-  <si>
-    <t>T-16</t>
-  </si>
-  <si>
-    <t>P-20</t>
-  </si>
-  <si>
-    <t>T-07</t>
-  </si>
-  <si>
-    <t>T-10</t>
-  </si>
-  <si>
-    <t>P-21</t>
-  </si>
-  <si>
-    <t>P-18</t>
-  </si>
-  <si>
-    <t>P-17</t>
-  </si>
-  <si>
-    <t>T-13</t>
+    <t>sem acesso</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>sem estrada até este talhão</t>
   </si>
   <si>
     <t>TOTAL / MÁXIMO</t>
@@ -220,7 +229,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -263,6 +272,17 @@
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -321,20 +341,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -349,13 +362,28 @@
     <xf numFmtId="4" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -724,31 +752,31 @@
         <v>12</v>
       </c>
       <c r="B5" s="5">
-        <v>93.91</v>
+        <v>59.49</v>
       </c>
       <c r="C5" s="6">
-        <v>4667</v>
+        <v>4192</v>
       </c>
       <c r="D5" s="7">
-        <v>9654</v>
+        <v>10950</v>
       </c>
       <c r="E5" s="7">
-        <v>3852</v>
+        <v>9173</v>
       </c>
       <c r="F5" s="7">
-        <v>3453</v>
+        <v>3468</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" ref="G5:G28" si="0">D5/1000</f>
-        <v>9.6539999999999999</v>
+        <f t="shared" ref="G5:G27" si="0">D5/1000</f>
+        <v>10.95</v>
       </c>
       <c r="H5" s="8">
-        <f t="shared" ref="H5:H28" si="1">E5/1000</f>
-        <v>3.8519999999999999</v>
+        <f t="shared" ref="H5:H27" si="1">E5/1000</f>
+        <v>9.173</v>
       </c>
       <c r="I5" s="9">
-        <f t="shared" ref="I5:I28" si="2">IFERROR(D5/F5,"")</f>
-        <v>2.7958297132927887</v>
+        <f t="shared" ref="I5:I27" si="2">IFERROR(D5/F5,"")</f>
+        <v>3.1574394463667819</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -757,31 +785,31 @@
         <v>13</v>
       </c>
       <c r="B6" s="12">
-        <v>205.66</v>
+        <v>165.19</v>
       </c>
       <c r="C6" s="13">
-        <v>5951</v>
+        <v>5893</v>
       </c>
       <c r="D6" s="14">
-        <v>9654</v>
+        <v>7986</v>
       </c>
       <c r="E6" s="14">
-        <v>2371</v>
+        <v>6282</v>
       </c>
       <c r="F6" s="14">
-        <v>2356</v>
+        <v>2870</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>9.6539999999999999</v>
+        <v>7.9859999999999998</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="1"/>
-        <v>2.371</v>
+        <v>6.282</v>
       </c>
       <c r="I6" s="16">
         <f t="shared" si="2"/>
-        <v>4.0976230899830224</v>
+        <v>2.7825783972125437</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -790,31 +818,31 @@
         <v>14</v>
       </c>
       <c r="B7" s="5">
-        <v>73.69</v>
+        <v>185.59</v>
       </c>
       <c r="C7" s="6">
-        <v>4875</v>
+        <v>6451</v>
       </c>
       <c r="D7" s="7">
-        <v>9544</v>
+        <v>7986</v>
       </c>
       <c r="E7" s="7">
-        <v>5906</v>
+        <v>5269</v>
       </c>
       <c r="F7" s="7">
-        <v>3796</v>
+        <v>2159</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>9.5440000000000005</v>
+        <v>7.9859999999999998</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>5.9059999999999997</v>
+        <v>5.2690000000000001</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>2.5142255005268703</v>
+        <v>3.6989346919870312</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -823,396 +851,396 @@
         <v>15</v>
       </c>
       <c r="B8" s="12">
-        <v>165.19</v>
+        <v>126.4</v>
       </c>
       <c r="C8" s="13">
-        <v>5893</v>
+        <v>4651</v>
       </c>
       <c r="D8" s="14">
-        <v>9544</v>
+        <v>7836</v>
       </c>
       <c r="E8" s="14">
-        <v>6307</v>
+        <v>6565</v>
       </c>
       <c r="F8" s="14">
-        <v>2870</v>
+        <v>3350</v>
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>9.5440000000000005</v>
+        <v>7.8360000000000003</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
-        <v>6.3070000000000004</v>
+        <v>6.5650000000000004</v>
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>3.3254355400696864</v>
+        <v>2.3391044776119405</v>
       </c>
       <c r="J8" s="17"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="5">
-        <v>126.4</v>
-      </c>
-      <c r="C9" s="6">
-        <v>4651</v>
-      </c>
-      <c r="D9" s="7">
-        <v>9011</v>
-      </c>
-      <c r="E9" s="7">
-        <v>4550</v>
-      </c>
-      <c r="F9" s="7">
-        <v>3350</v>
-      </c>
-      <c r="G9" s="8">
-        <f t="shared" si="0"/>
-        <v>9.0109999999999992</v>
-      </c>
-      <c r="H9" s="8">
-        <f t="shared" si="1"/>
-        <v>4.55</v>
-      </c>
-      <c r="I9" s="9">
-        <f t="shared" si="2"/>
-        <v>2.6898507462686565</v>
-      </c>
-      <c r="J9" s="10"/>
+      <c r="B9" s="19">
+        <v>73.69</v>
+      </c>
+      <c r="C9" s="20">
+        <v>4875</v>
+      </c>
+      <c r="D9" s="21">
+        <v>7660</v>
+      </c>
+      <c r="E9" s="21">
+        <v>5867</v>
+      </c>
+      <c r="F9" s="21">
+        <v>3796</v>
+      </c>
+      <c r="G9" s="22">
+        <f t="shared" si="0"/>
+        <v>7.66</v>
+      </c>
+      <c r="H9" s="22">
+        <f t="shared" si="1"/>
+        <v>5.867</v>
+      </c>
+      <c r="I9" s="23">
+        <f t="shared" si="2"/>
+        <v>2.017913593256059</v>
+      </c>
+      <c r="J9" s="24"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="5">
+        <v>205.66</v>
+      </c>
+      <c r="C10" s="6">
+        <v>5951</v>
+      </c>
+      <c r="D10" s="7">
+        <v>7586</v>
+      </c>
+      <c r="E10" s="7">
+        <v>5669</v>
+      </c>
+      <c r="F10" s="7">
+        <v>2356</v>
+      </c>
+      <c r="G10" s="8">
+        <f t="shared" si="0"/>
+        <v>7.5860000000000003</v>
+      </c>
+      <c r="H10" s="8">
+        <f t="shared" si="1"/>
+        <v>5.6689999999999996</v>
+      </c>
+      <c r="I10" s="9">
+        <f t="shared" si="2"/>
+        <v>3.2198641765704585</v>
+      </c>
+      <c r="J10" s="10"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="5">
         <v>202.95</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C11" s="6">
         <v>5923</v>
       </c>
-      <c r="D10" s="14">
-        <v>8484</v>
-      </c>
-      <c r="E10" s="14">
-        <v>1286</v>
-      </c>
-      <c r="F10" s="14">
+      <c r="D11" s="7">
+        <v>7586</v>
+      </c>
+      <c r="E11" s="7">
+        <v>5669</v>
+      </c>
+      <c r="F11" s="7">
         <v>1272</v>
       </c>
-      <c r="G10" s="15">
-        <f t="shared" si="0"/>
-        <v>8.484</v>
-      </c>
-      <c r="H10" s="15">
-        <f t="shared" si="1"/>
-        <v>1.286</v>
-      </c>
-      <c r="I10" s="16">
-        <f t="shared" si="2"/>
-        <v>6.6698113207547172</v>
-      </c>
-      <c r="J10" s="17"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="12">
-        <v>185.59</v>
-      </c>
-      <c r="C11" s="13">
-        <v>6451</v>
-      </c>
-      <c r="D11" s="14">
-        <v>8025</v>
-      </c>
-      <c r="E11" s="14">
-        <v>5294</v>
-      </c>
-      <c r="F11" s="14">
-        <v>2159</v>
-      </c>
-      <c r="G11" s="15">
-        <f t="shared" si="0"/>
-        <v>8.0250000000000004</v>
-      </c>
-      <c r="H11" s="15">
-        <f t="shared" si="1"/>
-        <v>5.2939999999999996</v>
-      </c>
-      <c r="I11" s="16">
-        <f t="shared" si="2"/>
-        <v>3.716998610467809</v>
-      </c>
-      <c r="J11" s="17"/>
+      <c r="G11" s="8">
+        <f t="shared" si="0"/>
+        <v>7.5860000000000003</v>
+      </c>
+      <c r="H11" s="8">
+        <f t="shared" si="1"/>
+        <v>5.6689999999999996</v>
+      </c>
+      <c r="I11" s="9">
+        <f t="shared" si="2"/>
+        <v>5.9638364779874218</v>
+      </c>
+      <c r="J11" s="10"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="5">
+        <v>141.49</v>
+      </c>
+      <c r="C12" s="6">
+        <v>7024</v>
+      </c>
+      <c r="D12" s="7">
+        <v>6796</v>
+      </c>
+      <c r="E12" s="7">
+        <v>3299</v>
+      </c>
+      <c r="F12" s="7">
+        <v>1843</v>
+      </c>
+      <c r="G12" s="8">
+        <f t="shared" si="0"/>
+        <v>6.7960000000000003</v>
+      </c>
+      <c r="H12" s="8">
+        <f t="shared" si="1"/>
+        <v>3.2989999999999999</v>
+      </c>
+      <c r="I12" s="9">
+        <f t="shared" si="2"/>
+        <v>3.6874660879001628</v>
+      </c>
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="19">
         <v>128.74</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C13" s="20">
         <v>4709</v>
       </c>
-      <c r="D12" s="21">
-        <v>7425</v>
-      </c>
-      <c r="E12" s="21">
-        <v>3020</v>
-      </c>
-      <c r="F12" s="21">
+      <c r="D13" s="21">
+        <v>6616</v>
+      </c>
+      <c r="E13" s="21">
+        <v>5574</v>
+      </c>
+      <c r="F13" s="21">
         <v>2722</v>
       </c>
-      <c r="G12" s="22">
-        <f t="shared" si="0"/>
-        <v>7.4249999999999998</v>
-      </c>
-      <c r="H12" s="22">
-        <f t="shared" si="1"/>
-        <v>3.02</v>
-      </c>
-      <c r="I12" s="23">
-        <f t="shared" si="2"/>
-        <v>2.7277736958119032</v>
-      </c>
-      <c r="J12" s="24"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="12">
+      <c r="G13" s="22">
+        <f t="shared" si="0"/>
+        <v>6.6159999999999997</v>
+      </c>
+      <c r="H13" s="22">
+        <f t="shared" si="1"/>
+        <v>5.5739999999999998</v>
+      </c>
+      <c r="I13" s="23">
+        <f t="shared" si="2"/>
+        <v>2.4305657604702424</v>
+      </c>
+      <c r="J13" s="24"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="5">
         <v>181.52</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C14" s="6">
         <v>7622</v>
       </c>
-      <c r="D13" s="14">
-        <v>7022</v>
-      </c>
-      <c r="E13" s="14">
-        <v>411</v>
-      </c>
-      <c r="F13" s="14">
+      <c r="D14" s="7">
+        <v>6493</v>
+      </c>
+      <c r="E14" s="7">
+        <v>4570</v>
+      </c>
+      <c r="F14" s="7">
         <v>258</v>
       </c>
-      <c r="G13" s="15">
-        <f t="shared" si="0"/>
-        <v>7.0220000000000002</v>
-      </c>
-      <c r="H13" s="15">
-        <f t="shared" si="1"/>
-        <v>0.41099999999999998</v>
-      </c>
-      <c r="I13" s="16">
-        <f t="shared" si="2"/>
-        <v>27.217054263565892</v>
-      </c>
-      <c r="J13" s="17"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="12">
-        <v>141.49</v>
-      </c>
-      <c r="C14" s="13">
-        <v>7024</v>
-      </c>
-      <c r="D14" s="14">
-        <v>7022</v>
-      </c>
-      <c r="E14" s="14">
-        <v>2091</v>
-      </c>
-      <c r="F14" s="14">
-        <v>1843</v>
-      </c>
-      <c r="G14" s="15">
-        <f t="shared" si="0"/>
-        <v>7.0220000000000002</v>
-      </c>
-      <c r="H14" s="15">
-        <f t="shared" si="1"/>
-        <v>2.0910000000000002</v>
-      </c>
-      <c r="I14" s="16">
-        <f t="shared" si="2"/>
-        <v>3.8100922409115574</v>
-      </c>
-      <c r="J14" s="17"/>
+      <c r="G14" s="8">
+        <f t="shared" si="0"/>
+        <v>6.4930000000000003</v>
+      </c>
+      <c r="H14" s="8">
+        <f t="shared" si="1"/>
+        <v>4.57</v>
+      </c>
+      <c r="I14" s="9">
+        <f t="shared" si="2"/>
+        <v>25.166666666666668</v>
+      </c>
+      <c r="J14" s="10"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="5">
-        <v>104.48</v>
-      </c>
-      <c r="C15" s="6">
-        <v>4116</v>
-      </c>
-      <c r="D15" s="7">
-        <v>6570</v>
-      </c>
-      <c r="E15" s="7">
-        <v>3557</v>
-      </c>
-      <c r="F15" s="7">
-        <v>2549</v>
-      </c>
-      <c r="G15" s="8">
-        <f t="shared" si="0"/>
-        <v>6.57</v>
-      </c>
-      <c r="H15" s="8">
-        <f t="shared" si="1"/>
-        <v>3.5569999999999999</v>
-      </c>
-      <c r="I15" s="9">
-        <f t="shared" si="2"/>
-        <v>2.5774813652412711</v>
-      </c>
-      <c r="J15" s="10"/>
+      <c r="B15" s="19">
+        <v>93.91</v>
+      </c>
+      <c r="C15" s="20">
+        <v>4667</v>
+      </c>
+      <c r="D15" s="21">
+        <v>5948</v>
+      </c>
+      <c r="E15" s="21">
+        <v>3436</v>
+      </c>
+      <c r="F15" s="21">
+        <v>3453</v>
+      </c>
+      <c r="G15" s="22">
+        <f t="shared" si="0"/>
+        <v>5.9480000000000004</v>
+      </c>
+      <c r="H15" s="22">
+        <f t="shared" si="1"/>
+        <v>3.4359999999999999</v>
+      </c>
+      <c r="I15" s="23">
+        <f t="shared" si="2"/>
+        <v>1.722560092673038</v>
+      </c>
+      <c r="J15" s="24"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="5">
+        <v>200.1</v>
+      </c>
+      <c r="C16" s="6">
+        <v>5875</v>
+      </c>
+      <c r="D16" s="7">
+        <v>5737</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2733</v>
+      </c>
+      <c r="F16" s="7">
+        <v>1280</v>
+      </c>
+      <c r="G16" s="8">
+        <f t="shared" si="0"/>
+        <v>5.7370000000000001</v>
+      </c>
+      <c r="H16" s="8">
+        <f t="shared" si="1"/>
+        <v>2.7330000000000001</v>
+      </c>
+      <c r="I16" s="9">
+        <f t="shared" si="2"/>
+        <v>4.4820312500000004</v>
+      </c>
+      <c r="J16" s="10"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="19">
+        <v>205.61</v>
+      </c>
+      <c r="C17" s="20">
+        <v>5931</v>
+      </c>
+      <c r="D17" s="21">
+        <v>5710</v>
+      </c>
+      <c r="E17" s="21">
+        <v>3808</v>
+      </c>
+      <c r="F17" s="21">
+        <v>2368</v>
+      </c>
+      <c r="G17" s="22">
+        <f t="shared" si="0"/>
+        <v>5.71</v>
+      </c>
+      <c r="H17" s="22">
+        <f t="shared" si="1"/>
+        <v>3.8079999999999998</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="shared" si="2"/>
+        <v>2.4113175675675675</v>
+      </c>
+      <c r="J17" s="24"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="5">
         <v>111.43</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C18" s="6">
         <v>5109</v>
       </c>
-      <c r="D16" s="14">
-        <v>6391</v>
-      </c>
-      <c r="E16" s="14">
-        <v>1998</v>
-      </c>
-      <c r="F16" s="14">
+      <c r="D18" s="7">
+        <v>5624</v>
+      </c>
+      <c r="E18" s="7">
+        <v>4917</v>
+      </c>
+      <c r="F18" s="7">
         <v>1838</v>
       </c>
-      <c r="G16" s="15">
-        <f t="shared" si="0"/>
-        <v>6.391</v>
-      </c>
-      <c r="H16" s="15">
-        <f t="shared" si="1"/>
-        <v>1.998</v>
-      </c>
-      <c r="I16" s="16">
-        <f t="shared" si="2"/>
-        <v>3.4771490750816105</v>
-      </c>
-      <c r="J16" s="17"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="5">
-        <v>59.49</v>
-      </c>
-      <c r="C17" s="6">
-        <v>4192</v>
-      </c>
-      <c r="D17" s="7">
-        <v>6046</v>
-      </c>
-      <c r="E17" s="7">
-        <v>3852</v>
-      </c>
-      <c r="F17" s="7">
-        <v>3468</v>
-      </c>
-      <c r="G17" s="8">
-        <f t="shared" si="0"/>
-        <v>6.0460000000000003</v>
-      </c>
-      <c r="H17" s="8">
-        <f t="shared" si="1"/>
-        <v>3.8519999999999999</v>
-      </c>
-      <c r="I17" s="9">
-        <f t="shared" si="2"/>
-        <v>1.743367935409458</v>
-      </c>
-      <c r="J17" s="10"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="19">
-        <v>205.61</v>
-      </c>
-      <c r="C18" s="20">
-        <v>5931</v>
-      </c>
-      <c r="D18" s="21">
-        <v>6046</v>
-      </c>
-      <c r="E18" s="21">
-        <v>2375</v>
-      </c>
-      <c r="F18" s="21">
-        <v>2368</v>
-      </c>
-      <c r="G18" s="22">
-        <f t="shared" si="0"/>
-        <v>6.0460000000000003</v>
-      </c>
-      <c r="H18" s="22">
-        <f t="shared" si="1"/>
-        <v>2.375</v>
-      </c>
-      <c r="I18" s="23">
-        <f t="shared" si="2"/>
-        <v>2.5532094594594597</v>
-      </c>
-      <c r="J18" s="24"/>
+      <c r="G18" s="8">
+        <f t="shared" si="0"/>
+        <v>5.6239999999999997</v>
+      </c>
+      <c r="H18" s="8">
+        <f t="shared" si="1"/>
+        <v>4.9169999999999998</v>
+      </c>
+      <c r="I18" s="9">
+        <f t="shared" si="2"/>
+        <v>3.059847660500544</v>
+      </c>
+      <c r="J18" s="10"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="12">
-        <v>94.93</v>
-      </c>
-      <c r="C19" s="13">
-        <v>4729</v>
-      </c>
-      <c r="D19" s="14">
-        <v>5885</v>
-      </c>
-      <c r="E19" s="14">
-        <v>200</v>
-      </c>
-      <c r="F19" s="14">
-        <v>179</v>
-      </c>
-      <c r="G19" s="15">
-        <f t="shared" si="0"/>
-        <v>5.8849999999999998</v>
-      </c>
-      <c r="H19" s="15">
-        <f t="shared" si="1"/>
-        <v>0.2</v>
-      </c>
-      <c r="I19" s="16">
-        <f t="shared" si="2"/>
-        <v>32.877094972067042</v>
-      </c>
-      <c r="J19" s="17"/>
+      <c r="B19" s="5">
+        <v>115.16</v>
+      </c>
+      <c r="C19" s="6">
+        <v>4391</v>
+      </c>
+      <c r="D19" s="7">
+        <v>5100</v>
+      </c>
+      <c r="E19" s="7">
+        <v>3215</v>
+      </c>
+      <c r="F19" s="7">
+        <v>1059</v>
+      </c>
+      <c r="G19" s="8">
+        <f t="shared" si="0"/>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H19" s="8">
+        <f t="shared" si="1"/>
+        <v>3.2149999999999999</v>
+      </c>
+      <c r="I19" s="9">
+        <f t="shared" si="2"/>
+        <v>4.8158640226628897</v>
+      </c>
+      <c r="J19" s="10"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
@@ -1225,316 +1253,315 @@
         <v>4914</v>
       </c>
       <c r="D20" s="14">
-        <v>5555</v>
+        <v>4790</v>
       </c>
       <c r="E20" s="14">
-        <v>2131</v>
+        <v>2084</v>
       </c>
       <c r="F20" s="14">
         <v>1828</v>
       </c>
       <c r="G20" s="15">
         <f t="shared" si="0"/>
-        <v>5.5549999999999997</v>
+        <v>4.79</v>
       </c>
       <c r="H20" s="15">
         <f t="shared" si="1"/>
-        <v>2.1309999999999998</v>
+        <v>2.0840000000000001</v>
       </c>
       <c r="I20" s="16">
         <f t="shared" si="2"/>
-        <v>3.038840262582057</v>
+        <v>2.6203501094091903</v>
       </c>
       <c r="J20" s="17"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="12">
-        <v>70.63</v>
-      </c>
-      <c r="C21" s="13">
-        <v>4030</v>
-      </c>
-      <c r="D21" s="14">
-        <v>5459</v>
-      </c>
-      <c r="E21" s="14">
-        <v>1035</v>
-      </c>
-      <c r="F21" s="14">
-        <v>591</v>
-      </c>
-      <c r="G21" s="15">
-        <f t="shared" si="0"/>
-        <v>5.4589999999999996</v>
-      </c>
-      <c r="H21" s="15">
-        <f t="shared" si="1"/>
-        <v>1.0349999999999999</v>
-      </c>
-      <c r="I21" s="16">
-        <f t="shared" si="2"/>
-        <v>9.2368866328257191</v>
-      </c>
-      <c r="J21" s="17"/>
+      <c r="B21" s="5">
+        <v>171.85</v>
+      </c>
+      <c r="C21" s="6">
+        <v>5764</v>
+      </c>
+      <c r="D21" s="7">
+        <v>4624</v>
+      </c>
+      <c r="E21" s="7">
+        <v>160</v>
+      </c>
+      <c r="F21" s="7">
+        <v>154</v>
+      </c>
+      <c r="G21" s="8">
+        <f t="shared" si="0"/>
+        <v>4.6239999999999997</v>
+      </c>
+      <c r="H21" s="8">
+        <f t="shared" si="1"/>
+        <v>0.16</v>
+      </c>
+      <c r="I21" s="9">
+        <f t="shared" si="2"/>
+        <v>30.025974025974026</v>
+      </c>
+      <c r="J21" s="10"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="12">
-        <v>115.16</v>
-      </c>
-      <c r="C22" s="13">
-        <v>4391</v>
-      </c>
-      <c r="D22" s="14">
-        <v>5456</v>
-      </c>
-      <c r="E22" s="14">
-        <v>1477</v>
-      </c>
-      <c r="F22" s="14">
-        <v>1059</v>
-      </c>
-      <c r="G22" s="15">
-        <f t="shared" si="0"/>
-        <v>5.4560000000000004</v>
-      </c>
-      <c r="H22" s="15">
-        <f t="shared" si="1"/>
-        <v>1.4770000000000001</v>
-      </c>
-      <c r="I22" s="16">
-        <f t="shared" si="2"/>
-        <v>5.1520302171860246</v>
-      </c>
-      <c r="J22" s="17"/>
+      <c r="B22" s="5">
+        <v>94.93</v>
+      </c>
+      <c r="C22" s="6">
+        <v>4729</v>
+      </c>
+      <c r="D22" s="7">
+        <v>2762</v>
+      </c>
+      <c r="E22" s="7">
+        <v>160</v>
+      </c>
+      <c r="F22" s="7">
+        <v>179</v>
+      </c>
+      <c r="G22" s="8">
+        <f t="shared" si="0"/>
+        <v>2.762</v>
+      </c>
+      <c r="H22" s="8">
+        <f t="shared" si="1"/>
+        <v>0.16</v>
+      </c>
+      <c r="I22" s="9">
+        <f t="shared" si="2"/>
+        <v>15.430167597765363</v>
+      </c>
+      <c r="J22" s="10"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="12">
-        <v>200.1</v>
-      </c>
-      <c r="C23" s="13">
-        <v>5875</v>
-      </c>
-      <c r="D23" s="14">
-        <v>5193</v>
-      </c>
-      <c r="E23" s="14">
-        <v>1286</v>
-      </c>
-      <c r="F23" s="14">
-        <v>1280</v>
-      </c>
-      <c r="G23" s="15">
-        <f t="shared" si="0"/>
-        <v>5.1929999999999996</v>
-      </c>
-      <c r="H23" s="15">
-        <f t="shared" si="1"/>
-        <v>1.286</v>
-      </c>
-      <c r="I23" s="16">
-        <f t="shared" si="2"/>
-        <v>4.0570312499999996</v>
-      </c>
-      <c r="J23" s="17"/>
+      <c r="B23" s="19">
+        <v>148.24</v>
+      </c>
+      <c r="C23" s="20">
+        <v>4904</v>
+      </c>
+      <c r="D23" s="21">
+        <v>2365</v>
+      </c>
+      <c r="E23" s="21">
+        <v>1464</v>
+      </c>
+      <c r="F23" s="21">
+        <v>1045</v>
+      </c>
+      <c r="G23" s="22">
+        <f t="shared" si="0"/>
+        <v>2.3650000000000002</v>
+      </c>
+      <c r="H23" s="22">
+        <f t="shared" si="1"/>
+        <v>1.464</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="2"/>
+        <v>2.263157894736842</v>
+      </c>
+      <c r="J23" s="24"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="12">
-        <v>171.85</v>
-      </c>
-      <c r="C24" s="13">
-        <v>5764</v>
-      </c>
-      <c r="D24" s="14">
-        <v>4974</v>
-      </c>
-      <c r="E24" s="14">
-        <v>175</v>
-      </c>
-      <c r="F24" s="14">
-        <v>154</v>
-      </c>
-      <c r="G24" s="15">
-        <f t="shared" si="0"/>
-        <v>4.9740000000000002</v>
-      </c>
-      <c r="H24" s="15">
-        <f t="shared" si="1"/>
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="I24" s="16">
-        <f t="shared" si="2"/>
-        <v>32.298701298701296</v>
-      </c>
-      <c r="J24" s="17"/>
+      <c r="B24" s="5">
+        <v>56.86</v>
+      </c>
+      <c r="C24" s="6">
+        <v>4026</v>
+      </c>
+      <c r="D24" s="7">
+        <v>2084</v>
+      </c>
+      <c r="E24" s="7">
+        <v>515</v>
+      </c>
+      <c r="F24" s="7">
+        <v>308</v>
+      </c>
+      <c r="G24" s="8">
+        <f t="shared" si="0"/>
+        <v>2.0840000000000001</v>
+      </c>
+      <c r="H24" s="8">
+        <f t="shared" si="1"/>
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="I24" s="9">
+        <f t="shared" si="2"/>
+        <v>6.7662337662337659</v>
+      </c>
+      <c r="J24" s="10"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="12">
-        <v>148.24</v>
-      </c>
-      <c r="C25" s="13">
-        <v>4904</v>
-      </c>
-      <c r="D25" s="14">
-        <v>4367</v>
-      </c>
-      <c r="E25" s="14">
-        <v>1506</v>
-      </c>
-      <c r="F25" s="14">
-        <v>1045</v>
-      </c>
-      <c r="G25" s="15">
-        <f t="shared" si="0"/>
-        <v>4.367</v>
-      </c>
-      <c r="H25" s="15">
-        <f t="shared" si="1"/>
-        <v>1.506</v>
-      </c>
-      <c r="I25" s="16">
-        <f t="shared" si="2"/>
-        <v>4.1789473684210527</v>
-      </c>
-      <c r="J25" s="17"/>
+      <c r="B25" s="19">
+        <v>136.31</v>
+      </c>
+      <c r="C25" s="20">
+        <v>4890</v>
+      </c>
+      <c r="D25" s="21">
+        <v>2053</v>
+      </c>
+      <c r="E25" s="21">
+        <v>1024</v>
+      </c>
+      <c r="F25" s="21">
+        <v>1018</v>
+      </c>
+      <c r="G25" s="22">
+        <f t="shared" si="0"/>
+        <v>2.0529999999999999</v>
+      </c>
+      <c r="H25" s="22">
+        <f t="shared" si="1"/>
+        <v>1.024</v>
+      </c>
+      <c r="I25" s="23">
+        <f t="shared" si="2"/>
+        <v>2.0166994106090375</v>
+      </c>
+      <c r="J25" s="24"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>33</v>
       </c>
       <c r="B26" s="12">
-        <v>136.31</v>
+        <v>70.63</v>
       </c>
       <c r="C26" s="13">
-        <v>4890</v>
+        <v>4030</v>
       </c>
       <c r="D26" s="14">
-        <v>4028</v>
+        <v>1723</v>
       </c>
       <c r="E26" s="14">
-        <v>1063</v>
+        <v>978</v>
       </c>
       <c r="F26" s="14">
-        <v>1018</v>
+        <v>591</v>
       </c>
       <c r="G26" s="15">
         <f t="shared" si="0"/>
-        <v>4.0279999999999996</v>
+        <v>1.7230000000000001</v>
       </c>
       <c r="H26" s="15">
         <f t="shared" si="1"/>
-        <v>1.0629999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I26" s="16">
         <f t="shared" si="2"/>
-        <v>3.956777996070727</v>
+        <v>2.9153976311336716</v>
       </c>
       <c r="J26" s="17"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="5">
         <v>113.44</v>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="6">
         <v>4389</v>
       </c>
-      <c r="D27" s="14">
-        <v>3432</v>
-      </c>
-      <c r="E27" s="14">
-        <v>305</v>
-      </c>
-      <c r="F27" s="14">
+      <c r="D27" s="7">
+        <v>1490</v>
+      </c>
+      <c r="E27" s="7">
+        <v>340</v>
+      </c>
+      <c r="F27" s="7">
         <v>240</v>
       </c>
-      <c r="G27" s="15">
-        <f t="shared" si="0"/>
-        <v>3.4319999999999999</v>
-      </c>
-      <c r="H27" s="15">
-        <f t="shared" si="1"/>
-        <v>0.30499999999999999</v>
-      </c>
-      <c r="I27" s="16">
-        <f t="shared" si="2"/>
-        <v>14.3</v>
-      </c>
-      <c r="J27" s="17"/>
+      <c r="G27" s="8">
+        <f t="shared" si="0"/>
+        <v>1.49</v>
+      </c>
+      <c r="H27" s="8">
+        <f t="shared" si="1"/>
+        <v>0.34</v>
+      </c>
+      <c r="I27" s="9">
+        <f t="shared" si="2"/>
+        <v>6.208333333333333</v>
+      </c>
+      <c r="J27" s="10"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="12">
-        <v>56.86</v>
-      </c>
-      <c r="C28" s="13">
-        <v>4026</v>
-      </c>
-      <c r="D28" s="14">
-        <v>3293</v>
-      </c>
-      <c r="E28" s="14">
-        <v>361</v>
-      </c>
-      <c r="F28" s="14">
-        <v>308</v>
-      </c>
-      <c r="G28" s="15">
-        <f t="shared" si="0"/>
-        <v>3.2930000000000001</v>
-      </c>
-      <c r="H28" s="15">
-        <f t="shared" si="1"/>
-        <v>0.36099999999999999</v>
-      </c>
-      <c r="I28" s="16">
-        <f t="shared" si="2"/>
-        <v>10.691558441558442</v>
-      </c>
-      <c r="J28" s="17"/>
+      <c r="B28" s="5">
+        <v>104.48</v>
+      </c>
+      <c r="C28" s="6">
+        <v>4116</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="F28" s="7">
+        <v>2549</v>
+      </c>
+      <c r="G28" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="H28" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="I28" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="J28" s="28" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="26">
+      <c r="A30" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="30">
         <f>SUM(B5:B28)</f>
-        <v>3174.7400000000002</v>
-      </c>
-      <c r="D30" s="27">
+        <v>3174.74</v>
+      </c>
+      <c r="D30" s="31">
         <f>MAX(D5:D28)</f>
-        <v>9654</v>
-      </c>
-      <c r="G30" s="28">
+        <v>10950</v>
+      </c>
+      <c r="G30" s="32">
         <f>IFERROR(MAX(G5:G28),"")</f>
-        <v>9.6539999999999999</v>
-      </c>
-      <c r="I30" s="29">
+        <v>10.95</v>
+      </c>
+      <c r="I30" s="33">
         <f>IFERROR(AVERAGE(I5:I28),"")</f>
-        <v>7.9043237915107118</v>
+        <v>6.0522740929838506</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="30" t="s">
-        <v>37</v>
+      <c r="A31" s="34" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1552,88 +1579,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
-        <v>38</v>
+      <c r="A1" s="35" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="33" t="s">
-        <v>40</v>
+      <c r="A3" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="33" t="s">
-        <v>42</v>
+      <c r="A4" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="33" t="s">
-        <v>44</v>
+      <c r="A5" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="33" t="s">
-        <v>46</v>
+      <c r="A6" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>48</v>
+      <c r="A7" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>50</v>
+      <c r="A8" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>52</v>
+      <c r="A9" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>54</v>
+      <c r="A10" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="33" t="s">
-        <v>56</v>
+      <c r="A11" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>58</v>
+      <c r="A12" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/FAZENDA_PANAMA_distancias.xlsx
+++ b/FAZENDA_PANAMA_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B40269-9DAF-4941-B7FD-0AB4DA4CE191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303E1CB8-BE59-4D66-AF5A-CB1233A595FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>FAZENDA PANAMA — distância dos talhões até a sede</t>
   </si>
@@ -72,66 +72,69 @@
     <t>Observação</t>
   </si>
   <si>
+    <t>P-23</t>
+  </si>
+  <si>
+    <t>T-03</t>
+  </si>
+  <si>
+    <t>P-19</t>
+  </si>
+  <si>
+    <t>T-06</t>
+  </si>
+  <si>
+    <t>T-09</t>
+  </si>
+  <si>
+    <t>T-05</t>
+  </si>
+  <si>
+    <t>T-08</t>
+  </si>
+  <si>
+    <t>T-07</t>
+  </si>
+  <si>
+    <t>T-04</t>
+  </si>
+  <si>
+    <t>T-02</t>
+  </si>
+  <si>
+    <t>P-15</t>
+  </si>
+  <si>
     <t>T-01</t>
   </si>
   <si>
-    <t>T-06</t>
-  </si>
-  <si>
-    <t>T-09</t>
-  </si>
-  <si>
-    <t>P-23</t>
-  </si>
-  <si>
-    <t>T-03</t>
-  </si>
-  <si>
-    <t>T-05</t>
-  </si>
-  <si>
-    <t>T-08</t>
-  </si>
-  <si>
     <t>T-12</t>
   </si>
   <si>
-    <t>P-19</t>
+    <t>P-22</t>
+  </si>
+  <si>
+    <t>T-14</t>
   </si>
   <si>
     <t>T-11</t>
   </si>
   <si>
-    <t>T-02</t>
-  </si>
-  <si>
-    <t>T-07</t>
-  </si>
-  <si>
-    <t>T-04</t>
-  </si>
-  <si>
-    <t>P-15</t>
+    <t>T-10</t>
   </si>
   <si>
     <t>P-20</t>
   </si>
   <si>
-    <t>T-14</t>
-  </si>
-  <si>
-    <t>T-10</t>
-  </si>
-  <si>
     <t>P-16</t>
   </si>
   <si>
+    <t>T-13</t>
+  </si>
+  <si>
     <t>P-21</t>
   </si>
   <si>
-    <t>T-13</t>
-  </si>
-  <si>
     <t>P-18</t>
   </si>
   <si>
@@ -139,18 +142,6 @@
   </si>
   <si>
     <t>P-17</t>
-  </si>
-  <si>
-    <t>P-22</t>
-  </si>
-  <si>
-    <t>sem acesso</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>sem estrada até este talhão</t>
   </si>
   <si>
     <t>TOTAL / MÁXIMO</t>
@@ -229,7 +220,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,17 +266,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FFC00000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
@@ -311,12 +291,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -341,13 +321,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -362,28 +349,13 @@
     <xf numFmtId="4" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -752,31 +724,31 @@
         <v>12</v>
       </c>
       <c r="B5" s="5">
-        <v>59.49</v>
+        <v>126.4</v>
       </c>
       <c r="C5" s="6">
-        <v>4192</v>
+        <v>4651</v>
       </c>
       <c r="D5" s="7">
-        <v>10950</v>
+        <v>7922</v>
       </c>
       <c r="E5" s="7">
-        <v>9173</v>
+        <v>6651</v>
       </c>
       <c r="F5" s="7">
-        <v>3468</v>
+        <v>3350</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" ref="G5:G27" si="0">D5/1000</f>
-        <v>10.95</v>
+        <f t="shared" ref="G5:G28" si="0">D5/1000</f>
+        <v>7.9219999999999997</v>
       </c>
       <c r="H5" s="8">
-        <f t="shared" ref="H5:H27" si="1">E5/1000</f>
-        <v>9.173</v>
+        <f t="shared" ref="H5:H28" si="1">E5/1000</f>
+        <v>6.6509999999999998</v>
       </c>
       <c r="I5" s="9">
-        <f t="shared" ref="I5:I27" si="2">IFERROR(D5/F5,"")</f>
-        <v>3.1574394463667819</v>
+        <f t="shared" ref="I5:I28" si="2">IFERROR(D5/F5,"")</f>
+        <v>2.3647761194029853</v>
       </c>
       <c r="J5" s="10"/>
     </row>
@@ -785,31 +757,31 @@
         <v>13</v>
       </c>
       <c r="B6" s="12">
-        <v>165.19</v>
+        <v>73.69</v>
       </c>
       <c r="C6" s="13">
-        <v>5893</v>
+        <v>4875</v>
       </c>
       <c r="D6" s="14">
-        <v>7986</v>
+        <v>7300</v>
       </c>
       <c r="E6" s="14">
-        <v>6282</v>
+        <v>5200</v>
       </c>
       <c r="F6" s="14">
-        <v>2870</v>
+        <v>3796</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>7.9859999999999998</v>
+        <v>7.3</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="1"/>
-        <v>6.282</v>
+        <v>5.2</v>
       </c>
       <c r="I6" s="16">
         <f t="shared" si="2"/>
-        <v>2.7825783972125437</v>
+        <v>1.9230769230769231</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -818,31 +790,31 @@
         <v>14</v>
       </c>
       <c r="B7" s="5">
-        <v>185.59</v>
+        <v>128.74</v>
       </c>
       <c r="C7" s="6">
-        <v>6451</v>
+        <v>4709</v>
       </c>
       <c r="D7" s="7">
-        <v>7986</v>
+        <v>6702</v>
       </c>
       <c r="E7" s="7">
-        <v>5269</v>
+        <v>5660</v>
       </c>
       <c r="F7" s="7">
-        <v>2159</v>
+        <v>2722</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
-        <v>7.9859999999999998</v>
+        <v>6.702</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="1"/>
-        <v>5.2690000000000001</v>
+        <v>5.66</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="2"/>
-        <v>3.6989346919870312</v>
+        <v>2.4621601763409258</v>
       </c>
       <c r="J7" s="10"/>
     </row>
@@ -851,717 +823,718 @@
         <v>15</v>
       </c>
       <c r="B8" s="12">
-        <v>126.4</v>
+        <v>165.19</v>
       </c>
       <c r="C8" s="13">
-        <v>4651</v>
+        <v>5893</v>
       </c>
       <c r="D8" s="14">
-        <v>7836</v>
+        <v>6558</v>
       </c>
       <c r="E8" s="14">
-        <v>6565</v>
+        <v>4090</v>
       </c>
       <c r="F8" s="14">
-        <v>3350</v>
+        <v>2870</v>
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>7.8360000000000003</v>
+        <v>6.5579999999999998</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
-        <v>6.5650000000000004</v>
+        <v>4.09</v>
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>2.3391044776119405</v>
+        <v>2.2850174216027876</v>
       </c>
       <c r="J8" s="17"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="19">
-        <v>73.69</v>
-      </c>
-      <c r="C9" s="20">
-        <v>4875</v>
-      </c>
-      <c r="D9" s="21">
-        <v>7660</v>
-      </c>
-      <c r="E9" s="21">
-        <v>5867</v>
-      </c>
-      <c r="F9" s="21">
-        <v>3796</v>
-      </c>
-      <c r="G9" s="22">
-        <f t="shared" si="0"/>
-        <v>7.66</v>
-      </c>
-      <c r="H9" s="22">
-        <f t="shared" si="1"/>
-        <v>5.867</v>
-      </c>
-      <c r="I9" s="23">
-        <f t="shared" si="2"/>
-        <v>2.017913593256059</v>
-      </c>
-      <c r="J9" s="24"/>
+      <c r="B9" s="5">
+        <v>185.59</v>
+      </c>
+      <c r="C9" s="6">
+        <v>6451</v>
+      </c>
+      <c r="D9" s="7">
+        <v>6259</v>
+      </c>
+      <c r="E9" s="7">
+        <v>3011</v>
+      </c>
+      <c r="F9" s="7">
+        <v>2159</v>
+      </c>
+      <c r="G9" s="8">
+        <f t="shared" si="0"/>
+        <v>6.2590000000000003</v>
+      </c>
+      <c r="H9" s="8">
+        <f t="shared" si="1"/>
+        <v>3.0110000000000001</v>
+      </c>
+      <c r="I9" s="9">
+        <f t="shared" si="2"/>
+        <v>2.8990273274664196</v>
+      </c>
+      <c r="J9" s="10"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="12">
         <v>205.66</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="13">
         <v>5951</v>
       </c>
-      <c r="D10" s="7">
-        <v>7586</v>
-      </c>
-      <c r="E10" s="7">
-        <v>5669</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="D10" s="14">
+        <v>5868</v>
+      </c>
+      <c r="E10" s="14">
+        <v>4090</v>
+      </c>
+      <c r="F10" s="14">
         <v>2356</v>
       </c>
-      <c r="G10" s="8">
-        <f t="shared" si="0"/>
-        <v>7.5860000000000003</v>
-      </c>
-      <c r="H10" s="8">
-        <f t="shared" si="1"/>
-        <v>5.6689999999999996</v>
-      </c>
-      <c r="I10" s="9">
-        <f t="shared" si="2"/>
-        <v>3.2198641765704585</v>
-      </c>
-      <c r="J10" s="10"/>
+      <c r="G10" s="15">
+        <f t="shared" si="0"/>
+        <v>5.8680000000000003</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="1"/>
+        <v>4.09</v>
+      </c>
+      <c r="I10" s="16">
+        <f t="shared" si="2"/>
+        <v>2.4906621392190154</v>
+      </c>
+      <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="19">
         <v>202.95</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="20">
         <v>5923</v>
       </c>
-      <c r="D11" s="7">
-        <v>7586</v>
-      </c>
-      <c r="E11" s="7">
-        <v>5669</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="D11" s="21">
+        <v>5868</v>
+      </c>
+      <c r="E11" s="21">
+        <v>3011</v>
+      </c>
+      <c r="F11" s="21">
         <v>1272</v>
       </c>
-      <c r="G11" s="8">
-        <f t="shared" si="0"/>
-        <v>7.5860000000000003</v>
-      </c>
-      <c r="H11" s="8">
-        <f t="shared" si="1"/>
-        <v>5.6689999999999996</v>
-      </c>
-      <c r="I11" s="9">
-        <f t="shared" si="2"/>
-        <v>5.9638364779874218</v>
-      </c>
-      <c r="J11" s="10"/>
+      <c r="G11" s="22">
+        <f t="shared" si="0"/>
+        <v>5.8680000000000003</v>
+      </c>
+      <c r="H11" s="22">
+        <f t="shared" si="1"/>
+        <v>3.0110000000000001</v>
+      </c>
+      <c r="I11" s="23">
+        <f t="shared" si="2"/>
+        <v>4.6132075471698117</v>
+      </c>
+      <c r="J11" s="24"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="5">
-        <v>141.49</v>
-      </c>
-      <c r="C12" s="6">
-        <v>7024</v>
-      </c>
-      <c r="D12" s="7">
-        <v>6796</v>
-      </c>
-      <c r="E12" s="7">
-        <v>3299</v>
-      </c>
-      <c r="F12" s="7">
-        <v>1843</v>
-      </c>
-      <c r="G12" s="8">
-        <f t="shared" si="0"/>
-        <v>6.7960000000000003</v>
-      </c>
-      <c r="H12" s="8">
-        <f t="shared" si="1"/>
-        <v>3.2989999999999999</v>
-      </c>
-      <c r="I12" s="9">
-        <f t="shared" si="2"/>
-        <v>3.6874660879001628</v>
-      </c>
-      <c r="J12" s="10"/>
+      <c r="B12" s="19">
+        <v>200.1</v>
+      </c>
+      <c r="C12" s="20">
+        <v>5875</v>
+      </c>
+      <c r="D12" s="21">
+        <v>5788</v>
+      </c>
+      <c r="E12" s="21">
+        <v>2783</v>
+      </c>
+      <c r="F12" s="21">
+        <v>1280</v>
+      </c>
+      <c r="G12" s="22">
+        <f t="shared" si="0"/>
+        <v>5.7880000000000003</v>
+      </c>
+      <c r="H12" s="22">
+        <f t="shared" si="1"/>
+        <v>2.7829999999999999</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="2"/>
+        <v>4.5218749999999996</v>
+      </c>
+      <c r="J12" s="24"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="19">
-        <v>128.74</v>
-      </c>
-      <c r="C13" s="20">
-        <v>4709</v>
-      </c>
-      <c r="D13" s="21">
-        <v>6616</v>
-      </c>
-      <c r="E13" s="21">
-        <v>5574</v>
-      </c>
-      <c r="F13" s="21">
-        <v>2722</v>
-      </c>
-      <c r="G13" s="22">
-        <f t="shared" si="0"/>
-        <v>6.6159999999999997</v>
-      </c>
-      <c r="H13" s="22">
-        <f t="shared" si="1"/>
-        <v>5.5739999999999998</v>
-      </c>
-      <c r="I13" s="23">
-        <f t="shared" si="2"/>
-        <v>2.4305657604702424</v>
-      </c>
-      <c r="J13" s="24"/>
+      <c r="B13" s="5">
+        <v>205.61</v>
+      </c>
+      <c r="C13" s="6">
+        <v>5931</v>
+      </c>
+      <c r="D13" s="7">
+        <v>5761</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2346</v>
+      </c>
+      <c r="F13" s="7">
+        <v>2368</v>
+      </c>
+      <c r="G13" s="8">
+        <f t="shared" si="0"/>
+        <v>5.7610000000000001</v>
+      </c>
+      <c r="H13" s="8">
+        <f t="shared" si="1"/>
+        <v>2.3460000000000001</v>
+      </c>
+      <c r="I13" s="9">
+        <f t="shared" si="2"/>
+        <v>2.4328547297297298</v>
+      </c>
+      <c r="J13" s="10"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="5">
-        <v>181.52</v>
-      </c>
-      <c r="C14" s="6">
-        <v>7622</v>
-      </c>
-      <c r="D14" s="7">
-        <v>6493</v>
-      </c>
-      <c r="E14" s="7">
-        <v>4570</v>
-      </c>
-      <c r="F14" s="7">
-        <v>258</v>
-      </c>
-      <c r="G14" s="8">
-        <f t="shared" si="0"/>
-        <v>6.4930000000000003</v>
-      </c>
-      <c r="H14" s="8">
-        <f t="shared" si="1"/>
-        <v>4.57</v>
-      </c>
-      <c r="I14" s="9">
-        <f t="shared" si="2"/>
-        <v>25.166666666666668</v>
-      </c>
-      <c r="J14" s="10"/>
+      <c r="B14" s="12">
+        <v>93.91</v>
+      </c>
+      <c r="C14" s="13">
+        <v>4667</v>
+      </c>
+      <c r="D14" s="14">
+        <v>5734</v>
+      </c>
+      <c r="E14" s="14">
+        <v>3438</v>
+      </c>
+      <c r="F14" s="14">
+        <v>3453</v>
+      </c>
+      <c r="G14" s="15">
+        <f t="shared" si="0"/>
+        <v>5.734</v>
+      </c>
+      <c r="H14" s="15">
+        <f t="shared" si="1"/>
+        <v>3.4380000000000002</v>
+      </c>
+      <c r="I14" s="16">
+        <f t="shared" si="2"/>
+        <v>1.6605849985519838</v>
+      </c>
+      <c r="J14" s="17"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="19">
-        <v>93.91</v>
+        <v>111.43</v>
       </c>
       <c r="C15" s="20">
-        <v>4667</v>
+        <v>5109</v>
       </c>
       <c r="D15" s="21">
-        <v>5948</v>
+        <v>5710</v>
       </c>
       <c r="E15" s="21">
-        <v>3436</v>
+        <v>5002</v>
       </c>
       <c r="F15" s="21">
-        <v>3453</v>
+        <v>1838</v>
       </c>
       <c r="G15" s="22">
         <f t="shared" si="0"/>
-        <v>5.9480000000000004</v>
+        <v>5.71</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" si="1"/>
-        <v>3.4359999999999999</v>
+        <v>5.0019999999999998</v>
       </c>
       <c r="I15" s="23">
         <f t="shared" si="2"/>
-        <v>1.722560092673038</v>
+        <v>3.1066376496191515</v>
       </c>
       <c r="J15" s="24"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="5">
-        <v>200.1</v>
-      </c>
-      <c r="C16" s="6">
-        <v>5875</v>
-      </c>
-      <c r="D16" s="7">
-        <v>5737</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2733</v>
-      </c>
-      <c r="F16" s="7">
-        <v>1280</v>
-      </c>
-      <c r="G16" s="8">
-        <f t="shared" si="0"/>
-        <v>5.7370000000000001</v>
-      </c>
-      <c r="H16" s="8">
-        <f t="shared" si="1"/>
-        <v>2.7330000000000001</v>
-      </c>
-      <c r="I16" s="9">
-        <f t="shared" si="2"/>
-        <v>4.4820312500000004</v>
-      </c>
-      <c r="J16" s="10"/>
+      <c r="B16" s="12">
+        <v>59.49</v>
+      </c>
+      <c r="C16" s="13">
+        <v>4192</v>
+      </c>
+      <c r="D16" s="14">
+        <v>5158</v>
+      </c>
+      <c r="E16" s="14">
+        <v>3438</v>
+      </c>
+      <c r="F16" s="14">
+        <v>3468</v>
+      </c>
+      <c r="G16" s="15">
+        <f t="shared" si="0"/>
+        <v>5.1580000000000004</v>
+      </c>
+      <c r="H16" s="15">
+        <f t="shared" si="1"/>
+        <v>3.4380000000000002</v>
+      </c>
+      <c r="I16" s="16">
+        <f t="shared" si="2"/>
+        <v>1.4873125720876585</v>
+      </c>
+      <c r="J16" s="17"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="19">
-        <v>205.61</v>
-      </c>
-      <c r="C17" s="20">
-        <v>5931</v>
-      </c>
-      <c r="D17" s="21">
-        <v>5710</v>
-      </c>
-      <c r="E17" s="21">
-        <v>3808</v>
-      </c>
-      <c r="F17" s="21">
-        <v>2368</v>
-      </c>
-      <c r="G17" s="22">
-        <f t="shared" si="0"/>
-        <v>5.71</v>
-      </c>
-      <c r="H17" s="22">
-        <f t="shared" si="1"/>
-        <v>3.8079999999999998</v>
-      </c>
-      <c r="I17" s="23">
-        <f t="shared" si="2"/>
-        <v>2.4113175675675675</v>
-      </c>
-      <c r="J17" s="24"/>
+      <c r="B17" s="5">
+        <v>141.49</v>
+      </c>
+      <c r="C17" s="6">
+        <v>7024</v>
+      </c>
+      <c r="D17" s="7">
+        <v>5111</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2144</v>
+      </c>
+      <c r="F17" s="7">
+        <v>1843</v>
+      </c>
+      <c r="G17" s="8">
+        <f t="shared" si="0"/>
+        <v>5.1109999999999998</v>
+      </c>
+      <c r="H17" s="8">
+        <f t="shared" si="1"/>
+        <v>2.1440000000000001</v>
+      </c>
+      <c r="I17" s="9">
+        <f t="shared" si="2"/>
+        <v>2.7731958762886597</v>
+      </c>
+      <c r="J17" s="10"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="5">
-        <v>111.43</v>
-      </c>
-      <c r="C18" s="6">
-        <v>5109</v>
-      </c>
-      <c r="D18" s="7">
-        <v>5624</v>
-      </c>
-      <c r="E18" s="7">
-        <v>4917</v>
-      </c>
-      <c r="F18" s="7">
-        <v>1838</v>
-      </c>
-      <c r="G18" s="8">
-        <f t="shared" si="0"/>
-        <v>5.6239999999999997</v>
-      </c>
-      <c r="H18" s="8">
-        <f t="shared" si="1"/>
-        <v>4.9169999999999998</v>
-      </c>
-      <c r="I18" s="9">
-        <f t="shared" si="2"/>
-        <v>3.059847660500544</v>
-      </c>
-      <c r="J18" s="10"/>
+      <c r="B18" s="12">
+        <v>104.48</v>
+      </c>
+      <c r="C18" s="13">
+        <v>4116</v>
+      </c>
+      <c r="D18" s="14">
+        <v>4932</v>
+      </c>
+      <c r="E18" s="14">
+        <v>4355</v>
+      </c>
+      <c r="F18" s="14">
+        <v>2549</v>
+      </c>
+      <c r="G18" s="15">
+        <f t="shared" si="0"/>
+        <v>4.9320000000000004</v>
+      </c>
+      <c r="H18" s="15">
+        <f t="shared" si="1"/>
+        <v>4.3550000000000004</v>
+      </c>
+      <c r="I18" s="16">
+        <f t="shared" si="2"/>
+        <v>1.9348764221263242</v>
+      </c>
+      <c r="J18" s="17"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="5">
+        <v>81.069999999999993</v>
+      </c>
+      <c r="C19" s="6">
+        <v>4914</v>
+      </c>
+      <c r="D19" s="7">
+        <v>4876</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2170</v>
+      </c>
+      <c r="F19" s="7">
+        <v>1828</v>
+      </c>
+      <c r="G19" s="8">
+        <f t="shared" si="0"/>
+        <v>4.8760000000000003</v>
+      </c>
+      <c r="H19" s="8">
+        <f t="shared" si="1"/>
+        <v>2.17</v>
+      </c>
+      <c r="I19" s="9">
+        <f t="shared" si="2"/>
+        <v>2.6673960612691467</v>
+      </c>
+      <c r="J19" s="10"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="19">
+        <v>181.52</v>
+      </c>
+      <c r="C20" s="20">
+        <v>7622</v>
+      </c>
+      <c r="D20" s="21">
+        <v>4755</v>
+      </c>
+      <c r="E20" s="21">
+        <v>555</v>
+      </c>
+      <c r="F20" s="21">
+        <v>258</v>
+      </c>
+      <c r="G20" s="22">
+        <f t="shared" si="0"/>
+        <v>4.7549999999999999</v>
+      </c>
+      <c r="H20" s="22">
+        <f t="shared" si="1"/>
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="I20" s="23">
+        <f t="shared" si="2"/>
+        <v>18.430232558139537</v>
+      </c>
+      <c r="J20" s="24"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="19">
+        <v>171.85</v>
+      </c>
+      <c r="C21" s="20">
+        <v>5764</v>
+      </c>
+      <c r="D21" s="21">
+        <v>4675</v>
+      </c>
+      <c r="E21" s="21">
+        <v>211</v>
+      </c>
+      <c r="F21" s="21">
+        <v>154</v>
+      </c>
+      <c r="G21" s="22">
+        <f t="shared" si="0"/>
+        <v>4.6749999999999998</v>
+      </c>
+      <c r="H21" s="22">
+        <f t="shared" si="1"/>
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="I21" s="23">
+        <f t="shared" si="2"/>
+        <v>30.357142857142858</v>
+      </c>
+      <c r="J21" s="24"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="19">
         <v>115.16</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C22" s="20">
         <v>4391</v>
       </c>
-      <c r="D19" s="7">
-        <v>5100</v>
-      </c>
-      <c r="E19" s="7">
-        <v>3215</v>
-      </c>
-      <c r="F19" s="7">
+      <c r="D22" s="21">
+        <v>4348</v>
+      </c>
+      <c r="E22" s="21">
+        <v>3245</v>
+      </c>
+      <c r="F22" s="21">
         <v>1059</v>
       </c>
-      <c r="G19" s="8">
-        <f t="shared" si="0"/>
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="H19" s="8">
-        <f t="shared" si="1"/>
-        <v>3.2149999999999999</v>
-      </c>
-      <c r="I19" s="9">
-        <f t="shared" si="2"/>
-        <v>4.8158640226628897</v>
-      </c>
-      <c r="J19" s="10"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="12">
-        <v>81.069999999999993</v>
-      </c>
-      <c r="C20" s="13">
-        <v>4914</v>
-      </c>
-      <c r="D20" s="14">
-        <v>4790</v>
-      </c>
-      <c r="E20" s="14">
-        <v>2084</v>
-      </c>
-      <c r="F20" s="14">
-        <v>1828</v>
-      </c>
-      <c r="G20" s="15">
-        <f t="shared" si="0"/>
-        <v>4.79</v>
-      </c>
-      <c r="H20" s="15">
-        <f t="shared" si="1"/>
-        <v>2.0840000000000001</v>
-      </c>
-      <c r="I20" s="16">
-        <f t="shared" si="2"/>
-        <v>2.6203501094091903</v>
-      </c>
-      <c r="J20" s="17"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="5">
-        <v>171.85</v>
-      </c>
-      <c r="C21" s="6">
-        <v>5764</v>
-      </c>
-      <c r="D21" s="7">
-        <v>4624</v>
-      </c>
-      <c r="E21" s="7">
-        <v>160</v>
-      </c>
-      <c r="F21" s="7">
-        <v>154</v>
-      </c>
-      <c r="G21" s="8">
-        <f t="shared" si="0"/>
-        <v>4.6239999999999997</v>
-      </c>
-      <c r="H21" s="8">
-        <f t="shared" si="1"/>
-        <v>0.16</v>
-      </c>
-      <c r="I21" s="9">
-        <f t="shared" si="2"/>
-        <v>30.025974025974026</v>
-      </c>
-      <c r="J21" s="10"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="5">
-        <v>94.93</v>
-      </c>
-      <c r="C22" s="6">
-        <v>4729</v>
-      </c>
-      <c r="D22" s="7">
-        <v>2762</v>
-      </c>
-      <c r="E22" s="7">
-        <v>160</v>
-      </c>
-      <c r="F22" s="7">
-        <v>179</v>
-      </c>
-      <c r="G22" s="8">
-        <f t="shared" si="0"/>
-        <v>2.762</v>
-      </c>
-      <c r="H22" s="8">
-        <f t="shared" si="1"/>
-        <v>0.16</v>
-      </c>
-      <c r="I22" s="9">
-        <f t="shared" si="2"/>
-        <v>15.430167597765363</v>
-      </c>
-      <c r="J22" s="10"/>
+      <c r="G22" s="22">
+        <f t="shared" si="0"/>
+        <v>4.3479999999999999</v>
+      </c>
+      <c r="H22" s="22">
+        <f t="shared" si="1"/>
+        <v>3.2450000000000001</v>
+      </c>
+      <c r="I22" s="23">
+        <f t="shared" si="2"/>
+        <v>4.1057601510859305</v>
+      </c>
+      <c r="J22" s="24"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
         <v>30</v>
       </c>
       <c r="B23" s="19">
+        <v>94.93</v>
+      </c>
+      <c r="C23" s="20">
+        <v>4729</v>
+      </c>
+      <c r="D23" s="21">
+        <v>2819</v>
+      </c>
+      <c r="E23" s="21">
+        <v>211</v>
+      </c>
+      <c r="F23" s="21">
+        <v>179</v>
+      </c>
+      <c r="G23" s="22">
+        <f t="shared" si="0"/>
+        <v>2.819</v>
+      </c>
+      <c r="H23" s="22">
+        <f t="shared" si="1"/>
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="I23" s="23">
+        <f t="shared" si="2"/>
+        <v>15.748603351955307</v>
+      </c>
+      <c r="J23" s="24"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="19">
+        <v>56.86</v>
+      </c>
+      <c r="C24" s="20">
+        <v>4026</v>
+      </c>
+      <c r="D24" s="21">
+        <v>2477</v>
+      </c>
+      <c r="E24" s="21">
+        <v>601</v>
+      </c>
+      <c r="F24" s="21">
+        <v>308</v>
+      </c>
+      <c r="G24" s="22">
+        <f t="shared" si="0"/>
+        <v>2.4769999999999999</v>
+      </c>
+      <c r="H24" s="22">
+        <f t="shared" si="1"/>
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="I24" s="23">
+        <f t="shared" si="2"/>
+        <v>8.0422077922077921</v>
+      </c>
+      <c r="J24" s="24"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="5">
         <v>148.24</v>
       </c>
-      <c r="C23" s="20">
+      <c r="C25" s="6">
         <v>4904</v>
       </c>
-      <c r="D23" s="21">
-        <v>2365</v>
-      </c>
-      <c r="E23" s="21">
-        <v>1464</v>
-      </c>
-      <c r="F23" s="21">
+      <c r="D25" s="7">
+        <v>2451</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1550</v>
+      </c>
+      <c r="F25" s="7">
         <v>1045</v>
       </c>
-      <c r="G23" s="22">
-        <f t="shared" si="0"/>
-        <v>2.3650000000000002</v>
-      </c>
-      <c r="H23" s="22">
-        <f t="shared" si="1"/>
-        <v>1.464</v>
-      </c>
-      <c r="I23" s="23">
-        <f t="shared" si="2"/>
-        <v>2.263157894736842</v>
-      </c>
-      <c r="J23" s="24"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="5">
-        <v>56.86</v>
-      </c>
-      <c r="C24" s="6">
-        <v>4026</v>
-      </c>
-      <c r="D24" s="7">
-        <v>2084</v>
-      </c>
-      <c r="E24" s="7">
-        <v>515</v>
-      </c>
-      <c r="F24" s="7">
-        <v>308</v>
-      </c>
-      <c r="G24" s="8">
-        <f t="shared" si="0"/>
-        <v>2.0840000000000001</v>
-      </c>
-      <c r="H24" s="8">
-        <f t="shared" si="1"/>
-        <v>0.51500000000000001</v>
-      </c>
-      <c r="I24" s="9">
-        <f t="shared" si="2"/>
-        <v>6.7662337662337659</v>
-      </c>
-      <c r="J24" s="10"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="19">
-        <v>136.31</v>
-      </c>
-      <c r="C25" s="20">
-        <v>4890</v>
-      </c>
-      <c r="D25" s="21">
-        <v>2053</v>
-      </c>
-      <c r="E25" s="21">
-        <v>1024</v>
-      </c>
-      <c r="F25" s="21">
-        <v>1018</v>
-      </c>
-      <c r="G25" s="22">
-        <f t="shared" si="0"/>
-        <v>2.0529999999999999</v>
-      </c>
-      <c r="H25" s="22">
-        <f t="shared" si="1"/>
-        <v>1.024</v>
-      </c>
-      <c r="I25" s="23">
-        <f t="shared" si="2"/>
-        <v>2.0166994106090375</v>
-      </c>
-      <c r="J25" s="24"/>
+      <c r="G25" s="8">
+        <f t="shared" si="0"/>
+        <v>2.4510000000000001</v>
+      </c>
+      <c r="H25" s="8">
+        <f t="shared" si="1"/>
+        <v>1.55</v>
+      </c>
+      <c r="I25" s="9">
+        <f t="shared" si="2"/>
+        <v>2.3454545454545452</v>
+      </c>
+      <c r="J25" s="10"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>33</v>
       </c>
       <c r="B26" s="12">
+        <v>136.31</v>
+      </c>
+      <c r="C26" s="13">
+        <v>4890</v>
+      </c>
+      <c r="D26" s="14">
+        <v>2093</v>
+      </c>
+      <c r="E26" s="14">
+        <v>1063</v>
+      </c>
+      <c r="F26" s="14">
+        <v>1018</v>
+      </c>
+      <c r="G26" s="15">
+        <f t="shared" si="0"/>
+        <v>2.093</v>
+      </c>
+      <c r="H26" s="15">
+        <f t="shared" si="1"/>
+        <v>1.0629999999999999</v>
+      </c>
+      <c r="I26" s="16">
+        <f t="shared" si="2"/>
+        <v>2.0559921414538311</v>
+      </c>
+      <c r="J26" s="17"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="19">
         <v>70.63</v>
       </c>
-      <c r="C26" s="13">
+      <c r="C27" s="20">
         <v>4030</v>
       </c>
-      <c r="D26" s="14">
-        <v>1723</v>
-      </c>
-      <c r="E26" s="14">
-        <v>978</v>
-      </c>
-      <c r="F26" s="14">
+      <c r="D27" s="21">
+        <v>1809</v>
+      </c>
+      <c r="E27" s="21">
+        <v>1064</v>
+      </c>
+      <c r="F27" s="21">
         <v>591</v>
       </c>
-      <c r="G26" s="15">
-        <f t="shared" si="0"/>
-        <v>1.7230000000000001</v>
-      </c>
-      <c r="H26" s="15">
-        <f t="shared" si="1"/>
-        <v>0.97799999999999998</v>
-      </c>
-      <c r="I26" s="16">
-        <f t="shared" si="2"/>
-        <v>2.9153976311336716</v>
-      </c>
-      <c r="J26" s="17"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="5">
+      <c r="G27" s="22">
+        <f t="shared" si="0"/>
+        <v>1.8089999999999999</v>
+      </c>
+      <c r="H27" s="22">
+        <f t="shared" si="1"/>
+        <v>1.0640000000000001</v>
+      </c>
+      <c r="I27" s="23">
+        <f t="shared" si="2"/>
+        <v>3.0609137055837565</v>
+      </c>
+      <c r="J27" s="24"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="19">
         <v>113.44</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C28" s="20">
         <v>4389</v>
       </c>
-      <c r="D27" s="7">
-        <v>1490</v>
-      </c>
-      <c r="E27" s="7">
-        <v>340</v>
-      </c>
-      <c r="F27" s="7">
+      <c r="D28" s="21">
+        <v>1576</v>
+      </c>
+      <c r="E28" s="21">
+        <v>426</v>
+      </c>
+      <c r="F28" s="21">
         <v>240</v>
       </c>
-      <c r="G27" s="8">
-        <f t="shared" si="0"/>
-        <v>1.49</v>
-      </c>
-      <c r="H27" s="8">
-        <f t="shared" si="1"/>
-        <v>0.34</v>
-      </c>
-      <c r="I27" s="9">
-        <f t="shared" si="2"/>
-        <v>6.208333333333333</v>
-      </c>
-      <c r="J27" s="10"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="5">
-        <v>104.48</v>
-      </c>
-      <c r="C28" s="6">
-        <v>4116</v>
-      </c>
-      <c r="D28" s="25" t="s">
+      <c r="G28" s="22">
+        <f t="shared" si="0"/>
+        <v>1.5760000000000001</v>
+      </c>
+      <c r="H28" s="22">
+        <f t="shared" si="1"/>
+        <v>0.42599999999999999</v>
+      </c>
+      <c r="I28" s="23">
+        <f t="shared" si="2"/>
+        <v>6.5666666666666664</v>
+      </c>
+      <c r="J28" s="24"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="E28" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="F28" s="7">
-        <v>2549</v>
-      </c>
-      <c r="G28" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="H28" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="I28" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="J28" s="28" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="30">
+      <c r="B30" s="26">
         <f>SUM(B5:B28)</f>
         <v>3174.74</v>
       </c>
-      <c r="D30" s="31">
+      <c r="D30" s="27">
         <f>MAX(D5:D28)</f>
-        <v>10950</v>
-      </c>
-      <c r="G30" s="32">
+        <v>7922</v>
+      </c>
+      <c r="G30" s="28">
         <f>IFERROR(MAX(G5:G28),"")</f>
-        <v>10.95</v>
-      </c>
-      <c r="I30" s="33">
+        <v>7.9219999999999997</v>
+      </c>
+      <c r="I30" s="29">
         <f>IFERROR(AVERAGE(I5:I28),"")</f>
-        <v>6.0522740929838506</v>
+        <v>5.4306514472350722</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="34" t="s">
-        <v>40</v>
+      <c r="A31" s="30" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1579,88 +1552,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="31" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="32" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+      <c r="B4" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="37" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="32" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="36" t="s">
+      <c r="B5" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="37" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="32" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="36" t="s">
+      <c r="B6" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="37" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="32" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="36" t="s">
+      <c r="B7" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="37" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="32" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="36" t="s">
+      <c r="B8" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="37" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="32" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="36" t="s">
+      <c r="B9" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="37" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="32" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="36" t="s">
+      <c r="B10" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="37" t="s">
+    </row>
+    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="32" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="36" t="s">
+      <c r="B11" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="37" t="s">
+    </row>
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="32" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+      <c r="B12" s="33" t="s">
         <v>58</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/FAZENDA_PANAMA_distancias.xlsx
+++ b/FAZENDA_PANAMA_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303E1CB8-BE59-4D66-AF5A-CB1233A595FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D73A82-778F-4D7A-ACBF-FB4336D581D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,43 +87,43 @@
     <t>T-09</t>
   </si>
   <si>
+    <t>T-02</t>
+  </si>
+  <si>
+    <t>P-15</t>
+  </si>
+  <si>
     <t>T-05</t>
   </si>
   <si>
+    <t>T-01</t>
+  </si>
+  <si>
+    <t>T-04</t>
+  </si>
+  <si>
+    <t>T-12</t>
+  </si>
+  <si>
+    <t>T-14</t>
+  </si>
+  <si>
+    <t>P-22</t>
+  </si>
+  <si>
+    <t>P-20</t>
+  </si>
+  <si>
     <t>T-08</t>
   </si>
   <si>
     <t>T-07</t>
   </si>
   <si>
-    <t>T-04</t>
-  </si>
-  <si>
-    <t>T-02</t>
-  </si>
-  <si>
-    <t>P-15</t>
-  </si>
-  <si>
-    <t>T-01</t>
-  </si>
-  <si>
-    <t>T-12</t>
-  </si>
-  <si>
-    <t>P-22</t>
-  </si>
-  <si>
-    <t>T-14</t>
-  </si>
-  <si>
     <t>T-11</t>
   </si>
   <si>
     <t>T-10</t>
-  </si>
-  <si>
-    <t>P-20</t>
   </si>
   <si>
     <t>P-16</t>
@@ -763,25 +763,25 @@
         <v>4875</v>
       </c>
       <c r="D6" s="14">
-        <v>7300</v>
+        <v>7290</v>
       </c>
       <c r="E6" s="14">
-        <v>5200</v>
+        <v>5190</v>
       </c>
       <c r="F6" s="14">
         <v>3796</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>7.3</v>
+        <v>7.29</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="1"/>
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="I6" s="16">
         <f t="shared" si="2"/>
-        <v>1.9230769230769231</v>
+        <v>1.9204425711275026</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -829,25 +829,25 @@
         <v>5893</v>
       </c>
       <c r="D8" s="14">
-        <v>6558</v>
+        <v>6548</v>
       </c>
       <c r="E8" s="14">
-        <v>4090</v>
+        <v>4078</v>
       </c>
       <c r="F8" s="14">
         <v>2870</v>
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>6.5579999999999998</v>
+        <v>6.548</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
-        <v>4.09</v>
+        <v>4.0780000000000003</v>
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>2.2850174216027876</v>
+        <v>2.2815331010452962</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -862,25 +862,25 @@
         <v>6451</v>
       </c>
       <c r="D9" s="7">
-        <v>6259</v>
+        <v>6237</v>
       </c>
       <c r="E9" s="7">
-        <v>3011</v>
+        <v>3001</v>
       </c>
       <c r="F9" s="7">
         <v>2159</v>
       </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
-        <v>6.2590000000000003</v>
+        <v>6.2370000000000001</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="1"/>
-        <v>3.0110000000000001</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="2"/>
-        <v>2.8990273274664196</v>
+        <v>2.8888374247336728</v>
       </c>
       <c r="J9" s="10"/>
     </row>
@@ -889,31 +889,31 @@
         <v>17</v>
       </c>
       <c r="B10" s="12">
-        <v>205.66</v>
+        <v>93.91</v>
       </c>
       <c r="C10" s="13">
-        <v>5951</v>
+        <v>4667</v>
       </c>
       <c r="D10" s="14">
-        <v>5868</v>
+        <v>5725</v>
       </c>
       <c r="E10" s="14">
-        <v>4090</v>
+        <v>3441</v>
       </c>
       <c r="F10" s="14">
-        <v>2356</v>
+        <v>3453</v>
       </c>
       <c r="G10" s="15">
         <f t="shared" si="0"/>
-        <v>5.8680000000000003</v>
+        <v>5.7249999999999996</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="1"/>
-        <v>4.09</v>
+        <v>3.4409999999999998</v>
       </c>
       <c r="I10" s="16">
         <f t="shared" si="2"/>
-        <v>2.4906621392190154</v>
+        <v>1.6579785693599769</v>
       </c>
       <c r="J10" s="17"/>
     </row>
@@ -922,97 +922,97 @@
         <v>18</v>
       </c>
       <c r="B11" s="19">
-        <v>202.95</v>
+        <v>111.43</v>
       </c>
       <c r="C11" s="20">
-        <v>5923</v>
+        <v>5109</v>
       </c>
       <c r="D11" s="21">
-        <v>5868</v>
+        <v>5710</v>
       </c>
       <c r="E11" s="21">
-        <v>3011</v>
+        <v>5003</v>
       </c>
       <c r="F11" s="21">
-        <v>1272</v>
+        <v>1838</v>
       </c>
       <c r="G11" s="22">
         <f t="shared" si="0"/>
-        <v>5.8680000000000003</v>
+        <v>5.71</v>
       </c>
       <c r="H11" s="22">
         <f t="shared" si="1"/>
-        <v>3.0110000000000001</v>
+        <v>5.0030000000000001</v>
       </c>
       <c r="I11" s="23">
         <f t="shared" si="2"/>
-        <v>4.6132075471698117</v>
+        <v>3.1066376496191515</v>
       </c>
       <c r="J11" s="24"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="19">
-        <v>200.1</v>
-      </c>
-      <c r="C12" s="20">
-        <v>5875</v>
-      </c>
-      <c r="D12" s="21">
-        <v>5788</v>
-      </c>
-      <c r="E12" s="21">
-        <v>2783</v>
-      </c>
-      <c r="F12" s="21">
-        <v>1280</v>
-      </c>
-      <c r="G12" s="22">
-        <f t="shared" si="0"/>
-        <v>5.7880000000000003</v>
-      </c>
-      <c r="H12" s="22">
-        <f t="shared" si="1"/>
-        <v>2.7829999999999999</v>
-      </c>
-      <c r="I12" s="23">
-        <f t="shared" si="2"/>
-        <v>4.5218749999999996</v>
-      </c>
-      <c r="J12" s="24"/>
+      <c r="B12" s="12">
+        <v>205.66</v>
+      </c>
+      <c r="C12" s="13">
+        <v>5951</v>
+      </c>
+      <c r="D12" s="14">
+        <v>5341</v>
+      </c>
+      <c r="E12" s="14">
+        <v>2335</v>
+      </c>
+      <c r="F12" s="14">
+        <v>2356</v>
+      </c>
+      <c r="G12" s="15">
+        <f t="shared" si="0"/>
+        <v>5.3410000000000002</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="1"/>
+        <v>2.335</v>
+      </c>
+      <c r="I12" s="16">
+        <f t="shared" si="2"/>
+        <v>2.2669779286926994</v>
+      </c>
+      <c r="J12" s="17"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="5">
-        <v>205.61</v>
+        <v>59.49</v>
       </c>
       <c r="C13" s="6">
-        <v>5931</v>
+        <v>4192</v>
       </c>
       <c r="D13" s="7">
-        <v>5761</v>
+        <v>5158</v>
       </c>
       <c r="E13" s="7">
-        <v>2346</v>
+        <v>3441</v>
       </c>
       <c r="F13" s="7">
-        <v>2368</v>
+        <v>3468</v>
       </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
-        <v>5.7610000000000001</v>
+        <v>5.1580000000000004</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="1"/>
-        <v>2.3460000000000001</v>
+        <v>3.4409999999999998</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="2"/>
-        <v>2.4328547297297298</v>
+        <v>1.4873125720876585</v>
       </c>
       <c r="J13" s="10"/>
     </row>
@@ -1021,97 +1021,97 @@
         <v>21</v>
       </c>
       <c r="B14" s="12">
-        <v>93.91</v>
+        <v>205.61</v>
       </c>
       <c r="C14" s="13">
-        <v>4667</v>
+        <v>5931</v>
       </c>
       <c r="D14" s="14">
-        <v>5734</v>
+        <v>5158</v>
       </c>
       <c r="E14" s="14">
-        <v>3438</v>
+        <v>2335</v>
       </c>
       <c r="F14" s="14">
-        <v>3453</v>
+        <v>2368</v>
       </c>
       <c r="G14" s="15">
         <f t="shared" si="0"/>
-        <v>5.734</v>
+        <v>5.1580000000000004</v>
       </c>
       <c r="H14" s="15">
         <f t="shared" si="1"/>
-        <v>3.4380000000000002</v>
+        <v>2.335</v>
       </c>
       <c r="I14" s="16">
         <f t="shared" si="2"/>
-        <v>1.6605849985519838</v>
+        <v>2.1782094594594597</v>
       </c>
       <c r="J14" s="17"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="19">
-        <v>111.43</v>
-      </c>
-      <c r="C15" s="20">
-        <v>5109</v>
-      </c>
-      <c r="D15" s="21">
-        <v>5710</v>
-      </c>
-      <c r="E15" s="21">
-        <v>5002</v>
-      </c>
-      <c r="F15" s="21">
-        <v>1838</v>
-      </c>
-      <c r="G15" s="22">
-        <f t="shared" si="0"/>
-        <v>5.71</v>
-      </c>
-      <c r="H15" s="22">
-        <f t="shared" si="1"/>
-        <v>5.0019999999999998</v>
-      </c>
-      <c r="I15" s="23">
-        <f t="shared" si="2"/>
-        <v>3.1066376496191515</v>
-      </c>
-      <c r="J15" s="24"/>
+      <c r="B15" s="5">
+        <v>141.49</v>
+      </c>
+      <c r="C15" s="6">
+        <v>7024</v>
+      </c>
+      <c r="D15" s="7">
+        <v>5102</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2140</v>
+      </c>
+      <c r="F15" s="7">
+        <v>1843</v>
+      </c>
+      <c r="G15" s="8">
+        <f t="shared" si="0"/>
+        <v>5.1020000000000003</v>
+      </c>
+      <c r="H15" s="8">
+        <f t="shared" si="1"/>
+        <v>2.14</v>
+      </c>
+      <c r="I15" s="9">
+        <f t="shared" si="2"/>
+        <v>2.7683125339120997</v>
+      </c>
+      <c r="J15" s="10"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="12">
-        <v>59.49</v>
+        <v>81.069999999999993</v>
       </c>
       <c r="C16" s="13">
-        <v>4192</v>
+        <v>4914</v>
       </c>
       <c r="D16" s="14">
-        <v>5158</v>
+        <v>4876</v>
       </c>
       <c r="E16" s="14">
-        <v>3438</v>
+        <v>2164</v>
       </c>
       <c r="F16" s="14">
-        <v>3468</v>
+        <v>1828</v>
       </c>
       <c r="G16" s="15">
         <f t="shared" si="0"/>
-        <v>5.1580000000000004</v>
+        <v>4.8760000000000003</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
-        <v>3.4380000000000002</v>
+        <v>2.1640000000000001</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="2"/>
-        <v>1.4873125720876585</v>
+        <v>2.6673960612691467</v>
       </c>
       <c r="J16" s="17"/>
     </row>
@@ -1120,130 +1120,130 @@
         <v>24</v>
       </c>
       <c r="B17" s="5">
-        <v>141.49</v>
+        <v>104.48</v>
       </c>
       <c r="C17" s="6">
-        <v>7024</v>
+        <v>4116</v>
       </c>
       <c r="D17" s="7">
-        <v>5111</v>
+        <v>4489</v>
       </c>
       <c r="E17" s="7">
-        <v>2144</v>
+        <v>3912</v>
       </c>
       <c r="F17" s="7">
-        <v>1843</v>
+        <v>2549</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>5.1109999999999998</v>
+        <v>4.4889999999999999</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="1"/>
-        <v>2.1440000000000001</v>
+        <v>3.9119999999999999</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="2"/>
-        <v>2.7731958762886597</v>
+        <v>1.7610827775598275</v>
       </c>
       <c r="J17" s="10"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="12">
-        <v>104.48</v>
-      </c>
-      <c r="C18" s="13">
-        <v>4116</v>
-      </c>
-      <c r="D18" s="14">
-        <v>4932</v>
-      </c>
-      <c r="E18" s="14">
-        <v>4355</v>
-      </c>
-      <c r="F18" s="14">
-        <v>2549</v>
-      </c>
-      <c r="G18" s="15">
-        <f t="shared" si="0"/>
-        <v>4.9320000000000004</v>
-      </c>
-      <c r="H18" s="15">
-        <f t="shared" si="1"/>
-        <v>4.3550000000000004</v>
-      </c>
-      <c r="I18" s="16">
-        <f t="shared" si="2"/>
-        <v>1.9348764221263242</v>
-      </c>
-      <c r="J18" s="17"/>
+      <c r="B18" s="19">
+        <v>115.16</v>
+      </c>
+      <c r="C18" s="20">
+        <v>4391</v>
+      </c>
+      <c r="D18" s="21">
+        <v>4343</v>
+      </c>
+      <c r="E18" s="21">
+        <v>3256</v>
+      </c>
+      <c r="F18" s="21">
+        <v>1059</v>
+      </c>
+      <c r="G18" s="22">
+        <f t="shared" si="0"/>
+        <v>4.343</v>
+      </c>
+      <c r="H18" s="22">
+        <f t="shared" si="1"/>
+        <v>3.2559999999999998</v>
+      </c>
+      <c r="I18" s="23">
+        <f t="shared" si="2"/>
+        <v>4.1010387157695938</v>
+      </c>
+      <c r="J18" s="24"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="5">
-        <v>81.069999999999993</v>
-      </c>
-      <c r="C19" s="6">
-        <v>4914</v>
-      </c>
-      <c r="D19" s="7">
-        <v>4876</v>
-      </c>
-      <c r="E19" s="7">
-        <v>2170</v>
-      </c>
-      <c r="F19" s="7">
-        <v>1828</v>
-      </c>
-      <c r="G19" s="8">
-        <f t="shared" si="0"/>
-        <v>4.8760000000000003</v>
-      </c>
-      <c r="H19" s="8">
-        <f t="shared" si="1"/>
-        <v>2.17</v>
-      </c>
-      <c r="I19" s="9">
-        <f t="shared" si="2"/>
-        <v>2.6673960612691467</v>
-      </c>
-      <c r="J19" s="10"/>
+      <c r="B19" s="19">
+        <v>202.95</v>
+      </c>
+      <c r="C19" s="20">
+        <v>5923</v>
+      </c>
+      <c r="D19" s="21">
+        <v>4156</v>
+      </c>
+      <c r="E19" s="21">
+        <v>1263</v>
+      </c>
+      <c r="F19" s="21">
+        <v>1272</v>
+      </c>
+      <c r="G19" s="22">
+        <f t="shared" si="0"/>
+        <v>4.1559999999999997</v>
+      </c>
+      <c r="H19" s="22">
+        <f t="shared" si="1"/>
+        <v>1.2629999999999999</v>
+      </c>
+      <c r="I19" s="23">
+        <f t="shared" si="2"/>
+        <v>3.2672955974842766</v>
+      </c>
+      <c r="J19" s="24"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="19">
-        <v>181.52</v>
+        <v>200.1</v>
       </c>
       <c r="C20" s="20">
-        <v>7622</v>
+        <v>5875</v>
       </c>
       <c r="D20" s="21">
-        <v>4755</v>
+        <v>4041</v>
       </c>
       <c r="E20" s="21">
-        <v>555</v>
+        <v>1263</v>
       </c>
       <c r="F20" s="21">
-        <v>258</v>
+        <v>1280</v>
       </c>
       <c r="G20" s="22">
         <f t="shared" si="0"/>
-        <v>4.7549999999999999</v>
+        <v>4.0410000000000004</v>
       </c>
       <c r="H20" s="22">
         <f t="shared" si="1"/>
-        <v>0.55500000000000005</v>
+        <v>1.2629999999999999</v>
       </c>
       <c r="I20" s="23">
         <f t="shared" si="2"/>
-        <v>18.430232558139537</v>
+        <v>3.1570312500000002</v>
       </c>
       <c r="J20" s="24"/>
     </row>
@@ -1252,31 +1252,31 @@
         <v>28</v>
       </c>
       <c r="B21" s="19">
-        <v>171.85</v>
+        <v>181.52</v>
       </c>
       <c r="C21" s="20">
-        <v>5764</v>
+        <v>7622</v>
       </c>
       <c r="D21" s="21">
-        <v>4675</v>
+        <v>3054</v>
       </c>
       <c r="E21" s="21">
-        <v>211</v>
+        <v>381</v>
       </c>
       <c r="F21" s="21">
-        <v>154</v>
+        <v>258</v>
       </c>
       <c r="G21" s="22">
         <f t="shared" si="0"/>
-        <v>4.6749999999999998</v>
+        <v>3.0539999999999998</v>
       </c>
       <c r="H21" s="22">
         <f t="shared" si="1"/>
-        <v>0.21099999999999999</v>
+        <v>0.38100000000000001</v>
       </c>
       <c r="I21" s="23">
         <f t="shared" si="2"/>
-        <v>30.357142857142858</v>
+        <v>11.837209302325581</v>
       </c>
       <c r="J21" s="24"/>
     </row>
@@ -1285,31 +1285,31 @@
         <v>29</v>
       </c>
       <c r="B22" s="19">
-        <v>115.16</v>
+        <v>171.85</v>
       </c>
       <c r="C22" s="20">
-        <v>4391</v>
+        <v>5764</v>
       </c>
       <c r="D22" s="21">
-        <v>4348</v>
+        <v>2943</v>
       </c>
       <c r="E22" s="21">
-        <v>3245</v>
+        <v>211</v>
       </c>
       <c r="F22" s="21">
-        <v>1059</v>
+        <v>154</v>
       </c>
       <c r="G22" s="22">
         <f t="shared" si="0"/>
-        <v>4.3479999999999999</v>
+        <v>2.9430000000000001</v>
       </c>
       <c r="H22" s="22">
         <f t="shared" si="1"/>
-        <v>3.2450000000000001</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="I22" s="23">
         <f t="shared" si="2"/>
-        <v>4.1057601510859305</v>
+        <v>19.11038961038961</v>
       </c>
       <c r="J22" s="24"/>
     </row>
@@ -1324,7 +1324,7 @@
         <v>4729</v>
       </c>
       <c r="D23" s="21">
-        <v>2819</v>
+        <v>2808</v>
       </c>
       <c r="E23" s="21">
         <v>211</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="G23" s="22">
         <f t="shared" si="0"/>
-        <v>2.819</v>
+        <v>2.8079999999999998</v>
       </c>
       <c r="H23" s="22">
         <f t="shared" si="1"/>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="I23" s="23">
         <f t="shared" si="2"/>
-        <v>15.748603351955307</v>
+        <v>15.687150837988828</v>
       </c>
       <c r="J23" s="24"/>
     </row>
@@ -1357,7 +1357,7 @@
         <v>4026</v>
       </c>
       <c r="D24" s="21">
-        <v>2477</v>
+        <v>2463</v>
       </c>
       <c r="E24" s="21">
         <v>601</v>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="G24" s="22">
         <f t="shared" si="0"/>
-        <v>2.4769999999999999</v>
+        <v>2.4630000000000001</v>
       </c>
       <c r="H24" s="22">
         <f t="shared" si="1"/>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="I24" s="23">
         <f t="shared" si="2"/>
-        <v>8.0422077922077921</v>
+        <v>7.9967532467532472</v>
       </c>
       <c r="J24" s="24"/>
     </row>
@@ -1390,25 +1390,25 @@
         <v>4904</v>
       </c>
       <c r="D25" s="7">
-        <v>2451</v>
+        <v>2325</v>
       </c>
       <c r="E25" s="7">
-        <v>1550</v>
+        <v>1424</v>
       </c>
       <c r="F25" s="7">
         <v>1045</v>
       </c>
       <c r="G25" s="8">
         <f t="shared" si="0"/>
-        <v>2.4510000000000001</v>
+        <v>2.3250000000000002</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="1"/>
-        <v>1.55</v>
+        <v>1.4239999999999999</v>
       </c>
       <c r="I25" s="9">
         <f t="shared" si="2"/>
-        <v>2.3454545454545452</v>
+        <v>2.2248803827751198</v>
       </c>
       <c r="J25" s="10"/>
     </row>
@@ -1446,37 +1446,37 @@
       <c r="J26" s="17"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="5">
         <v>70.63</v>
       </c>
-      <c r="C27" s="20">
+      <c r="C27" s="6">
         <v>4030</v>
       </c>
-      <c r="D27" s="21">
-        <v>1809</v>
-      </c>
-      <c r="E27" s="21">
-        <v>1064</v>
-      </c>
-      <c r="F27" s="21">
+      <c r="D27" s="7">
+        <v>1682</v>
+      </c>
+      <c r="E27" s="7">
+        <v>937</v>
+      </c>
+      <c r="F27" s="7">
         <v>591</v>
       </c>
-      <c r="G27" s="22">
-        <f t="shared" si="0"/>
-        <v>1.8089999999999999</v>
-      </c>
-      <c r="H27" s="22">
-        <f t="shared" si="1"/>
-        <v>1.0640000000000001</v>
-      </c>
-      <c r="I27" s="23">
-        <f t="shared" si="2"/>
-        <v>3.0609137055837565</v>
-      </c>
-      <c r="J27" s="24"/>
+      <c r="G27" s="8">
+        <f t="shared" si="0"/>
+        <v>1.6819999999999999</v>
+      </c>
+      <c r="H27" s="8">
+        <f t="shared" si="1"/>
+        <v>0.93700000000000006</v>
+      </c>
+      <c r="I27" s="9">
+        <f t="shared" si="2"/>
+        <v>2.8460236886632826</v>
+      </c>
+      <c r="J27" s="10"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
@@ -1489,25 +1489,25 @@
         <v>4389</v>
       </c>
       <c r="D28" s="21">
-        <v>1576</v>
+        <v>1449</v>
       </c>
       <c r="E28" s="21">
-        <v>426</v>
+        <v>283</v>
       </c>
       <c r="F28" s="21">
         <v>240</v>
       </c>
       <c r="G28" s="22">
         <f t="shared" si="0"/>
-        <v>1.5760000000000001</v>
+        <v>1.4490000000000001</v>
       </c>
       <c r="H28" s="22">
         <f t="shared" si="1"/>
-        <v>0.42599999999999999</v>
+        <v>0.28299999999999997</v>
       </c>
       <c r="I28" s="23">
         <f t="shared" si="2"/>
-        <v>6.5666666666666664</v>
+        <v>6.0374999999999996</v>
       </c>
       <c r="J28" s="24"/>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="I30" s="29">
         <f>IFERROR(AVERAGE(I5:I28),"")</f>
-        <v>5.4306514472350722</v>
+        <v>4.5055384049255736</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_PANAMA_distancias.xlsx
+++ b/FAZENDA_PANAMA_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D73A82-778F-4D7A-ACBF-FB4336D581D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB376409-9900-4CBD-BD36-F84BEDD0C367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/FAZENDA_PANAMA_distancias.xlsx
+++ b/FAZENDA_PANAMA_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB376409-9900-4CBD-BD36-F84BEDD0C367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B14AA9-7DD3-4D6A-8B76-1FEF447B257B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -763,25 +763,25 @@
         <v>4875</v>
       </c>
       <c r="D6" s="14">
-        <v>7290</v>
+        <v>7278</v>
       </c>
       <c r="E6" s="14">
-        <v>5190</v>
+        <v>5205</v>
       </c>
       <c r="F6" s="14">
         <v>3796</v>
       </c>
       <c r="G6" s="15">
         <f t="shared" si="0"/>
-        <v>7.29</v>
+        <v>7.2779999999999996</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" si="1"/>
-        <v>5.19</v>
+        <v>5.2050000000000001</v>
       </c>
       <c r="I6" s="16">
         <f t="shared" si="2"/>
-        <v>1.9204425711275026</v>
+        <v>1.9172813487881981</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -829,7 +829,7 @@
         <v>5893</v>
       </c>
       <c r="D8" s="14">
-        <v>6548</v>
+        <v>6546</v>
       </c>
       <c r="E8" s="14">
         <v>4078</v>
@@ -839,7 +839,7 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>6.548</v>
+        <v>6.5460000000000003</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="1"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="I8" s="16">
         <f t="shared" si="2"/>
-        <v>2.2815331010452962</v>
+        <v>2.2808362369337978</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -928,7 +928,7 @@
         <v>5109</v>
       </c>
       <c r="D11" s="21">
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="E11" s="21">
         <v>5003</v>
@@ -938,7 +938,7 @@
       </c>
       <c r="G11" s="22">
         <f t="shared" si="0"/>
-        <v>5.71</v>
+        <v>5.7110000000000003</v>
       </c>
       <c r="H11" s="22">
         <f t="shared" si="1"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="I11" s="23">
         <f t="shared" si="2"/>
-        <v>3.1066376496191515</v>
+        <v>3.1071817192600655</v>
       </c>
       <c r="J11" s="24"/>
     </row>
@@ -961,7 +961,7 @@
         <v>5951</v>
       </c>
       <c r="D12" s="14">
-        <v>5341</v>
+        <v>5262</v>
       </c>
       <c r="E12" s="14">
         <v>2335</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="G12" s="15">
         <f t="shared" si="0"/>
-        <v>5.3410000000000002</v>
+        <v>5.2619999999999996</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="1"/>
@@ -979,7 +979,7 @@
       </c>
       <c r="I12" s="16">
         <f t="shared" si="2"/>
-        <v>2.2669779286926994</v>
+        <v>2.2334465195246178</v>
       </c>
       <c r="J12" s="17"/>
     </row>
@@ -1096,7 +1096,7 @@
         <v>4876</v>
       </c>
       <c r="E16" s="14">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="F16" s="14">
         <v>1828</v>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="H16" s="15">
         <f t="shared" si="1"/>
-        <v>2.1640000000000001</v>
+        <v>2.165</v>
       </c>
       <c r="I16" s="16">
         <f t="shared" si="2"/>
@@ -1195,7 +1195,7 @@
         <v>4156</v>
       </c>
       <c r="E19" s="21">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="F19" s="21">
         <v>1272</v>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H19" s="22">
         <f t="shared" si="1"/>
-        <v>1.2629999999999999</v>
+        <v>1.262</v>
       </c>
       <c r="I19" s="23">
         <f t="shared" si="2"/>
@@ -1228,7 +1228,7 @@
         <v>4041</v>
       </c>
       <c r="E20" s="21">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="F20" s="21">
         <v>1280</v>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="H20" s="22">
         <f t="shared" si="1"/>
-        <v>1.2629999999999999</v>
+        <v>1.262</v>
       </c>
       <c r="I20" s="23">
         <f t="shared" si="2"/>
@@ -1489,7 +1489,7 @@
         <v>4389</v>
       </c>
       <c r="D28" s="21">
-        <v>1449</v>
+        <v>1661</v>
       </c>
       <c r="E28" s="21">
         <v>283</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G28" s="22">
         <f t="shared" si="0"/>
-        <v>1.4490000000000001</v>
+        <v>1.661</v>
       </c>
       <c r="H28" s="22">
         <f t="shared" si="1"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="I28" s="23">
         <f t="shared" si="2"/>
-        <v>6.0374999999999996</v>
+        <v>6.9208333333333334</v>
       </c>
       <c r="J28" s="24"/>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="I30" s="29">
         <f>IFERROR(AVERAGE(I5:I28),"")</f>
-        <v>4.5055384049255736</v>
+        <v>4.5408087343987136</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">

--- a/FAZENDA_PANAMA_distancias.xlsx
+++ b/FAZENDA_PANAMA_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B14AA9-7DD3-4D6A-8B76-1FEF447B257B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CF4E75-DEB3-497D-85AA-800BBDBB3CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2232" yWindow="2232" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>

--- a/FAZENDA_PANAMA_distancias.xlsx
+++ b/FAZENDA_PANAMA_distancias.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhao\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CF4E75-DEB3-497D-85AA-800BBDBB3CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DD72A8-4BDF-44C8-8817-35E2B6693B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2232" yWindow="2232" windowWidth="14100" windowHeight="9792" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>

--- a/FAZENDA_PANAMA_distancias.xlsx
+++ b/FAZENDA_PANAMA_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DD72A8-4BDF-44C8-8817-35E2B6693B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344B7CC7-89BD-46CF-B0AC-C049E6DA2165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/FAZENDA_PANAMA_distancias.xlsx
+++ b/FAZENDA_PANAMA_distancias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344B7CC7-89BD-46CF-B0AC-C049E6DA2165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270F86A1-D003-4454-8DF3-B8CCF23CBA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -232,49 +232,58 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">

--- a/FAZENDA_PANAMA_distancias.xlsx
+++ b/FAZENDA_PANAMA_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270F86A1-D003-4454-8DF3-B8CCF23CBA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACE961A-B714-46FA-94E9-9F11FD0B260E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40875" yWindow="3930" windowWidth="14100" windowHeight="9795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -232,58 +232,49 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">

--- a/FAZENDA_PANAMA_distancias.xlsx
+++ b/FAZENDA_PANAMA_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACE961A-B714-46FA-94E9-9F11FD0B260E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BA2D58-A2BD-4776-B79D-457B8390004D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40875" yWindow="3930" windowWidth="14100" windowHeight="9795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="11280" windowHeight="7836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -232,49 +232,58 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">

--- a/FAZENDA_PANAMA_distancias.xlsx
+++ b/FAZENDA_PANAMA_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BA2D58-A2BD-4776-B79D-457B8390004D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8B9A05-F072-41C7-8A10-080899B5A1E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="11280" windowHeight="7836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>

--- a/FAZENDA_PANAMA_distancias.xlsx
+++ b/FAZENDA_PANAMA_distancias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\talhoes-distancias\saidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8B9A05-F072-41C7-8A10-080899B5A1E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA72556F-682E-45D9-AD95-B7A2272C1492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Distâncias" sheetId="1" r:id="rId1"/>
@@ -232,58 +232,49 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
